--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UGit\cocos-creator38-demo\assets\翻译\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="zh-Hans-CN" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="543">
   <si>
     <t>key</t>
   </si>
@@ -1420,6 +1425,12 @@
   </si>
   <si>
     <t>防空兵</t>
+  </si>
+  <si>
+    <t>KeyJiJia</t>
+  </si>
+  <si>
+    <t>机甲</t>
   </si>
   <si>
     <t>KeyJiDi</t>
@@ -3046,7 +3057,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C287"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="68.625" customWidth="1"/>
@@ -5375,113 +5386,113 @@
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="21" t="s">
+      <c r="A212" s="23" t="s">
         <v>417</v>
       </c>
-      <c r="B212" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C212" s="21" t="s">
-        <v>187</v>
+      <c r="B212" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="C212" s="23" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B213" s="21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="21" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B214" s="21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B215" s="21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B218" s="21" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B219" s="21" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B220" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B221" s="21" t="s">
-        <v>427</v>
+        <v>205</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>427</v>
+        <v>205</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -5489,31 +5500,31 @@
         <v>428</v>
       </c>
       <c r="B222" s="21" t="s">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>207</v>
+        <v>429</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B223" s="21" t="s">
-        <v>430</v>
+        <v>207</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>430</v>
+        <v>207</v>
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="23" t="s">
+      <c r="A224" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="B224" s="23" t="s">
+      <c r="B224" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="C224" s="23" t="s">
+      <c r="C224" s="21" t="s">
         <v>432</v>
       </c>
     </row>
@@ -5540,24 +5551,24 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="24" t="s">
+      <c r="A227" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="B227" s="24" t="s">
+      <c r="B227" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="C227" s="24" t="s">
+      <c r="C227" s="23" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="23" t="s">
+      <c r="A228" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="B228" s="23" t="s">
+      <c r="B228" s="24" t="s">
         <v>440</v>
       </c>
-      <c r="C228" s="23" t="s">
+      <c r="C228" s="24" t="s">
         <v>440</v>
       </c>
     </row>
@@ -5628,13 +5639,13 @@
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="7" t="s">
+      <c r="A235" s="23" t="s">
         <v>453</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="23" t="s">
         <v>454</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="23" t="s">
         <v>454</v>
       </c>
     </row>
@@ -5716,7 +5727,7 @@
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" t="s">
+      <c r="A243" s="7" t="s">
         <v>469</v>
       </c>
       <c r="B243" t="s">
@@ -5804,7 +5815,7 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="7" t="s">
+      <c r="A251" t="s">
         <v>485</v>
       </c>
       <c r="B251" t="s">
@@ -5847,36 +5858,36 @@
         <v>492</v>
       </c>
     </row>
-    <row r="255" s="4" customFormat="1" spans="1:3">
-      <c r="A255" s="11" t="s">
+    <row r="255" spans="1:3">
+      <c r="A255" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="B255" t="s">
         <v>494</v>
       </c>
-      <c r="C255" s="9" t="s">
+      <c r="C255" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
-      <c r="A256" t="s">
+    <row r="256" s="4" customFormat="1" spans="1:3">
+      <c r="A256" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="B256" s="7" t="s">
+      <c r="B256" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="C256" s="7" t="s">
+      <c r="C256" s="9" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="257" s="4" customFormat="1" spans="1:3">
-      <c r="A257" s="11" t="s">
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
         <v>497</v>
       </c>
-      <c r="B257" s="25" t="s">
+      <c r="B257" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="C257" s="25" t="s">
+      <c r="C257" s="7" t="s">
         <v>498</v>
       </c>
     </row>
@@ -5884,43 +5895,43 @@
       <c r="A258" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="B258" s="9" t="s">
+      <c r="B258" s="25" t="s">
         <v>500</v>
       </c>
-      <c r="C258" s="9" t="s">
+      <c r="C258" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
-      <c r="A259" s="7" t="s">
-        <v>180</v>
+    <row r="259" s="4" customFormat="1" spans="1:3">
+      <c r="A259" s="11" t="s">
+        <v>501</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>181</v>
+        <v>502</v>
       </c>
       <c r="C259" s="9" t="s">
-        <v>181</v>
+        <v>502</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" s="7" t="s">
-        <v>501</v>
+        <v>180</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>502</v>
+        <v>181</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>502</v>
+        <v>181</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="C261" t="s">
+      <c r="C261" s="9" t="s">
         <v>504</v>
       </c>
     </row>
@@ -5937,24 +5948,24 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C263" s="9" t="s">
-        <v>183</v>
+        <v>507</v>
+      </c>
+      <c r="B263" t="s">
+        <v>508</v>
+      </c>
+      <c r="C263" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="7" t="s">
-        <v>507</v>
+        <v>182</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>508</v>
+        <v>183</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>508</v>
+        <v>183</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -5970,24 +5981,24 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="7" t="s">
-        <v>184</v>
+        <v>511</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>185</v>
+        <v>512</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>185</v>
+        <v>512</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" s="7" t="s">
-        <v>511</v>
+        <v>184</v>
       </c>
       <c r="B267" s="9" t="s">
-        <v>512</v>
+        <v>185</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>512</v>
+        <v>185</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -6005,33 +6016,33 @@
       <c r="A269" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="B269" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="C269" s="25" t="s">
-        <v>310</v>
+      <c r="B269" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B270" s="25" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C270" s="25" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B271" s="25" t="s">
-        <v>518</v>
+        <v>312</v>
       </c>
       <c r="C271" s="25" t="s">
-        <v>518</v>
+        <v>312</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -6039,21 +6050,21 @@
         <v>519</v>
       </c>
       <c r="B272" s="25" t="s">
-        <v>314</v>
+        <v>520</v>
       </c>
       <c r="C272" s="25" t="s">
-        <v>314</v>
+        <v>520</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B273" s="25" t="s">
-        <v>521</v>
+        <v>314</v>
       </c>
       <c r="C273" s="25" t="s">
-        <v>521</v>
+        <v>314</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -6061,21 +6072,21 @@
         <v>522</v>
       </c>
       <c r="B274" s="25" t="s">
-        <v>318</v>
+        <v>523</v>
       </c>
       <c r="C274" s="25" t="s">
-        <v>318</v>
+        <v>523</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B275" s="25" t="s">
-        <v>524</v>
+        <v>318</v>
       </c>
       <c r="C275" s="25" t="s">
-        <v>524</v>
+        <v>318</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -6115,32 +6126,32 @@
       <c r="A279" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C279" s="25" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="280" s="4" customFormat="1" spans="1:3">
+    <row r="280" spans="1:3">
       <c r="A280" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="B280" s="26" t="s">
+      <c r="B280" t="s">
         <v>534</v>
       </c>
-      <c r="C280" s="26" t="s">
+      <c r="C280" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" s="4" customFormat="1" spans="1:3">
       <c r="A281" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="B281" s="25" t="s">
+      <c r="B281" s="26" t="s">
         <v>536</v>
       </c>
-      <c r="C281" s="25" t="s">
+      <c r="C281" s="26" t="s">
         <v>536</v>
       </c>
     </row>
@@ -6148,15 +6159,15 @@
       <c r="A282" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="25" t="s">
         <v>538</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C282" s="25" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" t="s">
+      <c r="A283" s="7" t="s">
         <v>539</v>
       </c>
       <c r="B283" t="s">
@@ -6167,13 +6178,24 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="B284" s="27"/>
+      <c r="A284" t="s">
+        <v>541</v>
+      </c>
+      <c r="B284" t="s">
+        <v>542</v>
+      </c>
+      <c r="C284" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="285" spans="1:3">
       <c r="B285" s="27"/>
     </row>
     <row r="286" spans="1:3">
       <c r="B286" s="27"/>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="B287" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6183,7 +6205,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C2 A4:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UGit\cocos-creator38-demo\assets\翻译\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\比较\即时战略指挥客户端\assets\翻译\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="546">
   <si>
     <t>key</t>
   </si>
@@ -1865,6 +1865,15 @@
   <si>
     <t>乒</t>
   </si>
+  <si>
+    <t>Key机甲</t>
+  </si>
+  <si>
+    <t>MiaoShu_JiJia</t>
+  </si>
+  <si>
+    <t>英雄单位，杀敌获得经验升级血技能</t>
+  </si>
 </sst>
 </file>
 
@@ -1876,7 +1885,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="38">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1996,12 +2005,6 @@
     <font>
       <i/>
       <sz val="10.5"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFE4E4E4"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
@@ -2476,134 +2479,134 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2669,9 +2672,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3057,7 +3057,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C287"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="68.625" customWidth="1"/>
@@ -6189,13 +6189,26 @@
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="B285" s="27"/>
+      <c r="A285" t="s">
+        <v>543</v>
+      </c>
+      <c r="B285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C285" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="B286" s="27"/>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="B287" s="27"/>
+      <c r="A286" t="s">
+        <v>544</v>
+      </c>
+      <c r="B286" t="s">
+        <v>545</v>
+      </c>
+      <c r="C286" t="s">
+        <v>545</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6205,7 +6218,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C2 A4:B6" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\比较\即时战略指挥客户端\assets\翻译\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UGit\cocos-creator38-demo\assets\翻译\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="553">
   <si>
     <t>key</t>
   </si>
@@ -1805,6 +1805,27 @@
   </si>
   <si>
     <t>能量</t>
+  </si>
+  <si>
+    <t>AttrName_12</t>
+  </si>
+  <si>
+    <t>火箭弹</t>
+  </si>
+  <si>
+    <t>AttrName_13</t>
+  </si>
+  <si>
+    <t>AttrName_14</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>AttrName_15</t>
+  </si>
+  <si>
+    <t>火焰</t>
   </si>
   <si>
     <t>DangQian</t>
@@ -3057,7 +3078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C290"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="68.625" customWidth="1"/>
@@ -6112,102 +6133,146 @@
       </c>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="7" t="s">
+      <c r="A278" t="s">
         <v>529</v>
       </c>
-      <c r="B278" s="25" t="s">
+      <c r="B278" t="s">
         <v>530</v>
       </c>
-      <c r="C278" s="25" t="s">
+      <c r="C278" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="7" t="s">
+      <c r="A279" t="s">
         <v>531</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" t="s">
+        <v>408</v>
+      </c>
+      <c r="C279" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
         <v>532</v>
       </c>
-      <c r="C279" s="25" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="7" t="s">
+      <c r="B280" t="s">
         <v>533</v>
       </c>
-      <c r="B280" t="s">
+      <c r="C280" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
         <v>534</v>
       </c>
-      <c r="C280" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="281" s="4" customFormat="1" spans="1:3">
-      <c r="A281" s="7" t="s">
+      <c r="B281" t="s">
         <v>535</v>
       </c>
-      <c r="B281" s="26" t="s">
-        <v>536</v>
-      </c>
-      <c r="C281" s="26" t="s">
-        <v>536</v>
+      <c r="C281" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="B282" s="25" t="s">
         <v>537</v>
       </c>
-      <c r="B282" s="25" t="s">
-        <v>538</v>
-      </c>
       <c r="C282" s="25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="B283" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="B283" t="s">
+      <c r="C283" s="25" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="C283" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" t="s">
+      <c r="B284" t="s">
         <v>541</v>
       </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="285" s="4" customFormat="1" spans="1:3">
+      <c r="A285" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="C284" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" t="s">
+      <c r="B285" s="26" t="s">
         <v>543</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C285" s="26" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B286" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="C286" s="25" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B287" t="s">
+        <v>547</v>
+      </c>
+      <c r="C287" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
+        <v>548</v>
+      </c>
+      <c r="B288" t="s">
+        <v>549</v>
+      </c>
+      <c r="C288" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" t="s">
+        <v>550</v>
+      </c>
+      <c r="B289" t="s">
         <v>418</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C289" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
-      <c r="A286" t="s">
-        <v>544</v>
-      </c>
-      <c r="B286" t="s">
-        <v>545</v>
-      </c>
-      <c r="C286" t="s">
-        <v>545</v>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
+        <v>551</v>
+      </c>
+      <c r="B290" t="s">
+        <v>552</v>
+      </c>
+      <c r="C290" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="607">
   <si>
     <t>key</t>
   </si>
@@ -49,12 +49,6 @@
     <t>zh-Hans-CN</t>
   </si>
   <si>
-    <t>Loading</t>
-  </si>
-  <si>
-    <t>加载中……</t>
-  </si>
-  <si>
     <t>GameName</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
   </si>
   <si>
     <t>即时战略指挥公告/公告左.txt</t>
-  </si>
-  <si>
-    <t>LoginMainSvr</t>
   </si>
   <si>
     <t>LoginTestSvr</t>
@@ -109,66 +100,12 @@
 &lt;size=10&gt;看30秒广告送10单位和1000资源，提前关闭广告送2单位和80资源&lt;/size&gt;</t>
   </si>
   <si>
-    <t>DuoWanJiaHunZhan_ShaMo</t>
-  </si>
-  <si>
-    <t>多玩家混战（沙漠）
-&lt;size=10&gt;看30秒广告送10单位和1000资源，提前关闭广告送2单位和80资源&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t>YiDaYi</t>
-  </si>
-  <si>
-    <t>一打一（我是房主）
-&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t>YiDaYi_PvE</t>
-  </si>
-  <si>
-    <t>一打一（打电脑）
-&lt;size=12&gt;其他玩家可旁观您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t>ZhongYangFangShou_WanJiaHeZuo</t>
-  </si>
-  <si>
-    <t>中央防守 玩家合作（我是房主）
-&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t>JiaRuDuoRenZhanJu</t>
-  </si>
-  <si>
-    <t>加入其他玩家创建的多人战局
-&lt;size=12&gt;挑战其他玩家&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t>SiFangDuiZhan</t>
-  </si>
-  <si>
-    <t>四方对战（我是房主）
-&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
-  </si>
-  <si>
     <t>LeaveScene</t>
   </si>
   <si>
     <t>离开场景</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>RenZaiXian</t>
-  </si>
-  <si>
-    <t>人在线</t>
-  </si>
-  <si>
     <t>InputChat</t>
   </si>
   <si>
@@ -190,38 +127,7 @@
     <t>urlGameStrategy</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>即时战略指挥攻略/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>攻略</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.txt</t>
-    </r>
+    <t>即时战略指挥攻略/攻略.txt</t>
   </si>
   <si>
     <t>ConnectSuccess</t>
@@ -240,12 +146,6 @@
   </si>
   <si>
     <t>连接错误，您可以再试一次</t>
-  </si>
-  <si>
-    <t>ConnectClosed</t>
-  </si>
-  <si>
-    <t>连接已断开，已回到登录场景</t>
   </si>
   <si>
     <t>PleaseInputNickname</t>
@@ -292,6 +192,18 @@
     <t>输入昵称……</t>
   </si>
   <si>
+    <t>Loading</t>
+  </si>
+  <si>
+    <t>加载中……</t>
+  </si>
+  <si>
+    <t>ConnectClosed</t>
+  </si>
+  <si>
+    <t>连接已断开，已回到登录场景</t>
+  </si>
+  <si>
     <t>SinglePlayerBattle</t>
   </si>
   <si>
@@ -313,6 +225,12 @@
 &lt;size=12&gt;曲名、作者、版权&lt;/size&gt;</t>
   </si>
   <si>
+    <t>RenZaiXian</t>
+  </si>
+  <si>
+    <t>人在线</t>
+  </si>
+  <si>
     <t>BackToPreMenu</t>
   </si>
   <si>
@@ -340,72 +258,19 @@
     <t>AuthorWuYaProducer</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>乌鸦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Producer(QQ 2998975740)</t>
-    </r>
+    <t>乌鸦Producer(QQ 2998975740)</t>
   </si>
   <si>
     <t>AuthorXieYuBai</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>EinhornN7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>獬羽柏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(QQ 2990490699)</t>
-    </r>
+    <t>EinhornN7獬羽柏(QQ 2990490699)</t>
   </si>
   <si>
     <t>AuthorDianBoBaoji</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电波暴击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(QQ 1106551898)</t>
-    </r>
+    <t>电波暴击(QQ 1106551898)</t>
   </si>
   <si>
     <t>MusicShiJieYouHuiFuLeHePing</t>
@@ -534,18 +399,56 @@
     <t>虫族</t>
   </si>
   <si>
+    <t>YiDaYi</t>
+  </si>
+  <si>
+    <t>一打一（我是房主）
+&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>DuoWanJiaHunZhan_ShaMo</t>
+  </si>
+  <si>
+    <t>多玩家混战（沙漠）
+&lt;size=10&gt;看30秒广告送10单位和1000资源，提前关闭广告送2单位和80资源&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>ZhongYangFangShou</t>
+  </si>
+  <si>
+    <t>中央防守 玩家合作（我是房主）
+&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>JiaRuDuoRenZhanJu</t>
+  </si>
+  <si>
+    <t>加入其他玩家创建的多人战局
+&lt;size=12&gt;挑战其他玩家&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>SiFangDuiZhan</t>
+  </si>
+  <si>
+    <t>四方对战（我是房主）
+&lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>ZhongYangFangShou_WanJiaHeZuo</t>
+  </si>
+  <si>
+    <t>FanKongJiangZhan_Ren</t>
+  </si>
+  <si>
+    <t>反空降战（人）</t>
+  </si>
+  <si>
     <t>DanWeiJieShao_Ren</t>
   </si>
   <si>
     <t>单位介绍（人）</t>
   </si>
   <si>
-    <t>FanKongJiangZhan_Ren</t>
-  </si>
-  <si>
-    <t>反空降战（人）</t>
-  </si>
-  <si>
     <t>FangKongZhan_Ren</t>
   </si>
   <si>
@@ -636,16 +539,17 @@
     <t>输</t>
   </si>
   <si>
+    <t>TaiSui</t>
+  </si>
+  <si>
+    <t>太
+岁</t>
+  </si>
+  <si>
     <t>KuangXuan</t>
   </si>
   <si>
     <t>框选</t>
-  </si>
-  <si>
-    <t>XiangQinKuangXuang</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在屏幕上拖动出一个方框，选中框内所有的活动单位。&lt;br/&gt;  在左边的设置按钮（齿轮图标）里可以在&lt;color=#a0ff50&gt;正矩形框选&lt;/color&gt;模式和&lt;color=#a0ff50&gt;菱形框选&lt;/color&gt;模式之间切换</t>
   </si>
   <si>
     <t>JianZhuDanWei</t>
@@ -668,12 +572,6 @@
 工虫</t>
   </si>
   <si>
-    <t>XiangQingKongXianGongChengCheGongChong</t>
-  </si>
-  <si>
-    <t>每点击一次切换到下一个&lt;color=#a0ff50&gt;工程车&lt;/color&gt;或&lt;color=#a0ff50&gt;工虫&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>QuanBuZhanDouDanWei</t>
   </si>
   <si>
@@ -681,12 +579,6 @@
   战斗单位</t>
   </si>
   <si>
-    <t>XiangQingQuanBuZhanDouDanWei</t>
-  </si>
-  <si>
-    <t>选中所有可移动的战斗单位</t>
-  </si>
-  <si>
     <t>ZhanBao</t>
   </si>
   <si>
@@ -778,11 +670,10 @@
 塔</t>
   </si>
   <si>
-    <t>TaiSui</t>
-  </si>
-  <si>
-    <t>太
-岁</t>
+    <t>DeZhanJv</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 的战局</t>
   </si>
   <si>
     <t>QuXiaoXuanZhong</t>
@@ -791,19 +682,6 @@
     <t>取消选中</t>
   </si>
   <si>
-    <t>XiangQingQuXiaoXuanZhong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    取消当前选中的单位。
-    可以防止误操作。</t>
-  </si>
-  <si>
-    <t>DeZhanJv</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 的战局</t>
-  </si>
-  <si>
     <t>JingTiKuang</t>
   </si>
   <si>
@@ -834,34 +712,19 @@
     <t>取  消</t>
   </si>
   <si>
-    <t>XiangQingQuXiao</t>
-  </si>
-  <si>
-    <t>取消当前操作</t>
-  </si>
-  <si>
-    <t>QueDingDianJiDianMian</t>
+    <t>LoginMainSvr</t>
+  </si>
+  <si>
+    <t>QueDing</t>
   </si>
   <si>
     <t>确 定</t>
   </si>
   <si>
-    <t>XiangQingQueDingDianJiDianMian</t>
-  </si>
-  <si>
-    <t>确定点击地面操作</t>
-  </si>
-  <si>
     <t>QiangXingZou</t>
   </si>
   <si>
     <t>强行走</t>
-  </si>
-  <si>
-    <t>XiangQingQiangXingZou</t>
-  </si>
-  <si>
-    <t>不理会途中遇到的敌人，强行走到目标点</t>
   </si>
   <si>
     <t>YuanDiJianShou</t>
@@ -871,22 +734,10 @@
 坚守</t>
   </si>
   <si>
-    <t>XiangQingYuanDiJianShou</t>
-  </si>
-  <si>
-    <t>不再追击警戒距离内的敌人</t>
-  </si>
-  <si>
     <t>GenSui</t>
   </si>
   <si>
     <t>跟随</t>
-  </si>
-  <si>
-    <t>XiangQingGenSui</t>
-  </si>
-  <si>
-    <t>跟随目标移动</t>
   </si>
   <si>
     <t>XunLuo</t>
@@ -896,12 +747,6 @@
 逻</t>
   </si>
   <si>
-    <t>XiangQingXunLuo</t>
-  </si>
-  <si>
-    <t>在选中的多个巡逻点之间巡逻</t>
-  </si>
-  <si>
     <t>LiKaiDiBao</t>
   </si>
   <si>
@@ -909,34 +754,16 @@
 地堡</t>
   </si>
   <si>
-    <t>XiangQingLiKaiDiBao</t>
-  </si>
-  <si>
-    <t>让&lt;color=#a0ff50&gt;地堡&lt;/color&gt;里的单位都出来</t>
-  </si>
-  <si>
     <t>LiKaiFangChong</t>
   </si>
   <si>
     <t>离开房虫</t>
   </si>
   <si>
-    <t>XiangQingLiKaiFangChong</t>
-  </si>
-  <si>
-    <t>让&lt;color=#a0ff50&gt;房虫&lt;/color&gt;里的单位都出来</t>
-  </si>
-  <si>
     <t>JiJieDian</t>
   </si>
   <si>
     <t>集结点</t>
-  </si>
-  <si>
-    <t>XiangQingJiJieDian</t>
-  </si>
-  <si>
-    <t>设置此建筑新产出单位的集结位置点</t>
   </si>
   <si>
     <t>GongChengCheJiJieDian</t>
@@ -946,12 +773,6 @@
 集结点</t>
   </si>
   <si>
-    <t>XiangQingGongChengCheJiJieDian</t>
-  </si>
-  <si>
-    <t>设置此建筑新产出工程车的集结位置点，如果把目标点设置到资源上，会自动采集目标资源</t>
-  </si>
-  <si>
     <t>GongChongJiJieDian</t>
   </si>
   <si>
@@ -959,12 +780,6 @@
 集结点</t>
   </si>
   <si>
-    <t>XiangQingGongChongJiJieDian</t>
-  </si>
-  <si>
-    <t>设置此建筑新产出工虫的集结位置点，如果把目标点设置到资源上，会自动采集目标资源</t>
-  </si>
-  <si>
     <t>FangChongJiJieDian</t>
   </si>
   <si>
@@ -972,15 +787,6 @@
 集结点</t>
   </si>
   <si>
-    <t>XiangQingFangChongJiJieDian</t>
-  </si>
-  <si>
-    <t>设置此建筑新产出房虫的集结位置点，如果把目标点设置到资源上，会自动采集目标资源</t>
-  </si>
-  <si>
-    <t>设置此建筑新产出房虫的集结位置点</t>
-  </si>
-  <si>
     <t>JieSuoJinZhanBing</t>
   </si>
   <si>
@@ -988,23 +794,11 @@
 近战兵</t>
   </si>
   <si>
-    <t>XiangQingJieSuoJinZhanBing</t>
-  </si>
-  <si>
-    <t>解锁后允许在兵营里产出&lt;color=#a0ff50&gt;近战兵&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>JieSuoQiangChong</t>
   </si>
   <si>
     <t>解锁
 枪虫</t>
-  </si>
-  <si>
-    <t>XiangQingJieSuoQiangChong</t>
-  </si>
-  <si>
-    <t>解锁后允许幼虫蜕变为&lt;color=#a0ff50&gt;枪虫&lt;/color&gt;</t>
   </si>
   <si>
     <t>ShengJiQiangBingGongJi</t>
@@ -1078,12 +872,6 @@
 分裂</t>
   </si>
   <si>
-    <t>XiangQingTaiSuiFenLie</t>
-  </si>
-  <si>
-    <t>分裂出一个新的太岁放置到源太岁的苔蔓(wàn)上</t>
-  </si>
-  <si>
     <t>ShanChuDanWei</t>
   </si>
   <si>
@@ -1091,340 +879,1003 @@
 单位</t>
   </si>
   <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>ZaiKanKan</t>
+  </si>
+  <si>
+    <t>再看看</t>
+  </si>
+  <si>
+    <t>GongJi</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>FangYu</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>YiDongSuDu</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>JingJieJvLi</t>
+  </si>
+  <si>
+    <t>警戒距离</t>
+  </si>
+  <si>
+    <t>GongJiJvLi</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>GongJiQianYao</t>
+  </si>
+  <si>
+    <t>攻击前摇</t>
+  </si>
+  <si>
+    <t>GongJiHouYao</t>
+  </si>
+  <si>
+    <t>攻击后摇</t>
+  </si>
+  <si>
+    <t>HaoMiao</t>
+  </si>
+  <si>
+    <t>毫秒</t>
+  </si>
+  <si>
+    <t>ChuShiHP</t>
+  </si>
+  <si>
+    <t>初始HP</t>
+  </si>
+  <si>
+    <t>MiaoShu_FangDun</t>
+  </si>
+  <si>
+    <t>永久阻挡，不会损坏</t>
+  </si>
+  <si>
+    <t>MiaoShu_GongChengChe</t>
+  </si>
+  <si>
+    <t>可采集资源，可建造建筑</t>
+  </si>
+  <si>
+    <t>MiaoShu_QiangBing</t>
+  </si>
+  <si>
+    <t>远程攻击</t>
+  </si>
+  <si>
+    <t>MiaoShu_JinZhanBing</t>
+  </si>
+  <si>
+    <t>近程攻击</t>
+  </si>
+  <si>
+    <t>MiaoShu_SanSeTanKe</t>
+  </si>
+  <si>
+    <t>超远距离范围攻击，前摇较长，克制炮台。爆炸溅射可能会伤害己方单位。</t>
+  </si>
+  <si>
+    <t>MiaoShu_GongChong</t>
+  </si>
+  <si>
+    <t>可采集资源，可变成建筑</t>
+  </si>
+  <si>
+    <t>MiaoShu_FeiJi</t>
+  </si>
+  <si>
+    <t>可飞越障碍物</t>
+  </si>
+  <si>
+    <t>MiaoShu_YouChong</t>
+  </si>
+  <si>
+    <t>可蜕变为其它活动单位</t>
+  </si>
+  <si>
+    <t>MiaoShu_LvSeTanKe</t>
+  </si>
+  <si>
+    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
+  </si>
+  <si>
+    <t>MiaoShu_FangChong</t>
+  </si>
+  <si>
+    <t>可增加活动单位上限</t>
+  </si>
+  <si>
+    <t>MiaoShu_FeiChong</t>
+  </si>
+  <si>
+    <t>可飞跃障碍物</t>
+  </si>
+  <si>
+    <t>MiaoShu_YiLiaoBing</t>
+  </si>
+  <si>
+    <t>可给友方单位恢复HP</t>
+  </si>
+  <si>
+    <t>MiaoShu_FangKongBing</t>
+  </si>
+  <si>
+    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
+  </si>
+  <si>
+    <t>MiaoShu_JiDi</t>
+  </si>
+  <si>
+    <t>可产出工程车</t>
+  </si>
+  <si>
+    <t>MiaoShu_BingYing</t>
+  </si>
+  <si>
+    <t>可产出枪兵和近战兵</t>
+  </si>
+  <si>
+    <t>MiaoShu_DiBao</t>
+  </si>
+  <si>
+    <t>高HP，可派遣步兵进入地堡</t>
+  </si>
+  <si>
+    <t>MiaoShu_PaoTai</t>
+  </si>
+  <si>
+    <t>克制除了坦克以外的一切单位</t>
+  </si>
+  <si>
+    <t>MiaoShu_ChongChao</t>
+  </si>
+  <si>
+    <t>可产出幼虫</t>
+  </si>
+  <si>
+    <t>MiaoShu_JiChang</t>
+  </si>
+  <si>
+    <t>可产出飞机</t>
+  </si>
+  <si>
+    <t>MiaoShu_ZhongCheChang</t>
+  </si>
+  <si>
+    <t>可产出三色坦克</t>
+  </si>
+  <si>
+    <t>MiaoShu_ChongYing</t>
+  </si>
+  <si>
+    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>MiaoShu_FeiTa</t>
+  </si>
+  <si>
+    <t>飞虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>MiaoShu_NiTaiYuan</t>
+  </si>
+  <si>
+    <t>绿色坦克的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>MiaoShu_TaiSui</t>
+  </si>
+  <si>
+    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
+  </si>
+  <si>
+    <t>Key特效</t>
+  </si>
+  <si>
+    <t>特效</t>
+  </si>
+  <si>
+    <t>Key视口</t>
+  </si>
+  <si>
+    <t>视口</t>
+  </si>
+  <si>
+    <t>Key苔蔓(wàn)</t>
+  </si>
+  <si>
+    <t>苔蔓(wàn)</t>
+  </si>
+  <si>
+    <t>Key工程车</t>
+  </si>
+  <si>
+    <t>工程车</t>
+  </si>
+  <si>
+    <t>Key枪兵</t>
+  </si>
+  <si>
+    <t>枪兵</t>
+  </si>
+  <si>
+    <t>Key近战兵</t>
+  </si>
+  <si>
+    <t>近战兵</t>
+  </si>
+  <si>
+    <t>Key三色坦克</t>
+  </si>
+  <si>
+    <t>三色坦克</t>
+  </si>
+  <si>
+    <t>Key工虫</t>
+  </si>
+  <si>
+    <t>工虫</t>
+  </si>
+  <si>
+    <t>Key飞机</t>
+  </si>
+  <si>
+    <t>飞机</t>
+  </si>
+  <si>
+    <t>Key枪虫</t>
+  </si>
+  <si>
+    <t>枪虫</t>
+  </si>
+  <si>
+    <t>Key近战虫</t>
+  </si>
+  <si>
+    <t>近战虫</t>
+  </si>
+  <si>
+    <t>Key幼虫</t>
+  </si>
+  <si>
+    <t>幼虫</t>
+  </si>
+  <si>
+    <t>Key绿色坦克</t>
+  </si>
+  <si>
+    <t>绿色坦克</t>
+  </si>
+  <si>
+    <t>Key光刺</t>
+  </si>
+  <si>
+    <t>光刺</t>
+  </si>
+  <si>
+    <t>Key房虫</t>
+  </si>
+  <si>
+    <t>房虫</t>
+  </si>
+  <si>
+    <t>Key飞虫</t>
+  </si>
+  <si>
+    <t>飞虫</t>
+  </si>
+  <si>
+    <t>Key医疗兵</t>
+  </si>
+  <si>
+    <t>医疗兵</t>
+  </si>
+  <si>
+    <t>Key防空兵</t>
+  </si>
+  <si>
+    <t>防空兵</t>
+  </si>
+  <si>
+    <t>Key飞塔</t>
+  </si>
+  <si>
+    <t>飞塔</t>
+  </si>
+  <si>
+    <t>Key太岁</t>
+  </si>
+  <si>
+    <t>太岁</t>
+  </si>
+  <si>
+    <t>Key枪虫怪</t>
+  </si>
+  <si>
+    <t>枪虫怪</t>
+  </si>
+  <si>
+    <t>Key近战虫怪</t>
+  </si>
+  <si>
+    <t>近战虫怪</t>
+  </si>
+  <si>
+    <t>Key工虫怪</t>
+  </si>
+  <si>
+    <t>工虫怪</t>
+  </si>
+  <si>
+    <t>Key枪兵怪</t>
+  </si>
+  <si>
+    <t>枪兵怪</t>
+  </si>
+  <si>
+    <t>Key近战兵怪</t>
+  </si>
+  <si>
+    <t>近战兵怪</t>
+  </si>
+  <si>
+    <t>Key工程车怪</t>
+  </si>
+  <si>
+    <t>工程车怪</t>
+  </si>
+  <si>
+    <t>Key幼虫怪</t>
+  </si>
+  <si>
+    <t>幼虫怪</t>
+  </si>
+  <si>
+    <t>Key飞虫怪</t>
+  </si>
+  <si>
+    <t>飞虫怪</t>
+  </si>
+  <si>
+    <t>Key绿色坦克怪</t>
+  </si>
+  <si>
+    <t>绿色坦克怪</t>
+  </si>
+  <si>
+    <t>Key房虫怪</t>
+  </si>
+  <si>
+    <t>房虫怪</t>
+  </si>
+  <si>
+    <t>Key防空兵怪</t>
+  </si>
+  <si>
+    <t>防空兵怪</t>
+  </si>
+  <si>
+    <t>MiaoShu_QiangChong</t>
+  </si>
+  <si>
+    <t>MiaoShu_JinZhanChong</t>
+  </si>
+  <si>
+    <t>MiaoShu_MinFang</t>
+  </si>
+  <si>
+    <t>Key方墩</t>
+  </si>
+  <si>
+    <t>Key晶体矿</t>
+  </si>
+  <si>
+    <t>Key燃气矿</t>
+  </si>
+  <si>
+    <t>Key基地</t>
+  </si>
+  <si>
+    <t>Key兵营</t>
+  </si>
+  <si>
+    <t>Key民房</t>
+  </si>
+  <si>
+    <t>Key地堡</t>
+  </si>
+  <si>
+    <t>Key炮台</t>
+  </si>
+  <si>
+    <t>Key虫巢</t>
+  </si>
+  <si>
+    <t>Key机场</t>
+  </si>
+  <si>
+    <t>Key重车厂</t>
+  </si>
+  <si>
+    <t>Key虫营</t>
+  </si>
+  <si>
+    <t>Key拟态源</t>
+  </si>
+  <si>
+    <t>Mi_Miao</t>
+  </si>
+  <si>
+    <t>米/秒</t>
+  </si>
+  <si>
+    <t>QingDianJiDiMianZhiZhiJianZhu</t>
+  </si>
+  <si>
+    <t>请点击地面放置建筑</t>
+  </si>
+  <si>
+    <t>QingDianJiDiMianZhiZhiXunLvDian</t>
+  </si>
+  <si>
+    <t>请点击地面设置巡逻点</t>
+  </si>
+  <si>
+    <t>QingDianJiDiMianZhiZhiQiangZouXingDiMuDi</t>
+  </si>
+  <si>
+    <t>强行走过程不会攻击敌人，请点击地面确定目的地</t>
+  </si>
+  <si>
+    <t>QingDianJiDiMianZhiZhiSheZhiCiJianZhuChanChuHuoDongDanWeiDeJiJiDian</t>
+  </si>
+  <si>
+    <t>请点击地面设置此建筑产出活动单位的集结点</t>
+  </si>
+  <si>
+    <t>QingZaiPingMuShangTuoDongYiKuangXuanDanWei</t>
+  </si>
+  <si>
+    <t>请在屏幕上拖动以框选单位</t>
+  </si>
+  <si>
+    <t>QingZaiXuanZhongTaiShuiDeTaiManWanShangFangZhiFenLieDeTaiShui</t>
+  </si>
+  <si>
+    <t>请在选中太岁的苔蔓(wàn)上放置分裂的太岁</t>
+  </si>
+  <si>
+    <t>SheZhi</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>JingTouTouYing</t>
+  </si>
+  <si>
+    <t>镜头投影</t>
+  </si>
+  <si>
+    <t>KuangXuanMoShi</t>
+  </si>
+  <si>
+    <t>框选模式</t>
+  </si>
+  <si>
+    <t>ShiKouFangDa</t>
+  </si>
+  <si>
+    <t>视口放大</t>
+  </si>
+  <si>
+    <t>ShiKouSuoXiao</t>
+  </si>
+  <si>
+    <t>视口缩小</t>
+  </si>
+  <si>
+    <t>DianJiZhuiJiaZuanZhong</t>
+  </si>
+  <si>
+    <t>点击单位都是追加选中</t>
+  </si>
+  <si>
+    <t>XianShiMingZi</t>
+  </si>
+  <si>
+    <t>显示名字</t>
+  </si>
+  <si>
+    <t>MingZiXianShiDanWeiLeiXing</t>
+  </si>
+  <si>
+    <t>名字里显示单位类型</t>
+  </si>
+  <si>
+    <t>LingXingKuangXuan</t>
+  </si>
+  <si>
+    <t>菱形框选</t>
+  </si>
+  <si>
+    <t>ZhengJuXingKuangXuan</t>
+  </si>
+  <si>
+    <t>正矩形框选</t>
+  </si>
+  <si>
+    <t>MoShi</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>YiQieHuanDao</t>
+  </si>
+  <si>
+    <t>已切换到</t>
+  </si>
+  <si>
+    <t>YiTianJiaWeiXunLvDian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 已添加为巡逻点，请继续点击地面添加巡逻点，或点击“确定”提交巡逻点列表</t>
+  </si>
+  <si>
+    <t>KeyTeXiao</t>
+  </si>
+  <si>
+    <t>KeyShiKou</t>
+  </si>
+  <si>
+    <t>KeyTaiWan</t>
+  </si>
+  <si>
+    <t>KeyFangDun</t>
+  </si>
+  <si>
+    <t>KeyJingTiKuang</t>
+  </si>
+  <si>
+    <t>KeyRanQiKuang</t>
+  </si>
+  <si>
+    <t>KeyGongChengChe</t>
+  </si>
+  <si>
+    <t>KeyQiangBing</t>
+  </si>
+  <si>
+    <t>KeyJinZhanBing</t>
+  </si>
+  <si>
+    <t>KeySanSeTanKe</t>
+  </si>
+  <si>
+    <t>KeyGongChong</t>
+  </si>
+  <si>
+    <t>KeyFeiJi</t>
+  </si>
+  <si>
+    <t>KeyQiangChong</t>
+  </si>
+  <si>
+    <t>KeyJinZhanChong</t>
+  </si>
+  <si>
+    <t>KeyYouChong</t>
+  </si>
+  <si>
+    <t>KeyLvSeTanKe</t>
+  </si>
+  <si>
+    <t>KeyGuangCi</t>
+  </si>
+  <si>
+    <t>KeyFangChong</t>
+  </si>
+  <si>
+    <t>KeyFeiChong</t>
+  </si>
+  <si>
+    <t>KeyYiLiaoBing</t>
+  </si>
+  <si>
+    <t>KeyFangKongBing</t>
+  </si>
+  <si>
+    <t>KeyJiDi</t>
+  </si>
+  <si>
+    <t>KeyBingYing</t>
+  </si>
+  <si>
+    <t>KeyMinFang</t>
+  </si>
+  <si>
+    <t>KeyDiBao</t>
+  </si>
+  <si>
+    <t>KeyPaoTai</t>
+  </si>
+  <si>
+    <t>KeyChongChao</t>
+  </si>
+  <si>
+    <t>KeyJiChang</t>
+  </si>
+  <si>
+    <t>KeyZhongCheChang</t>
+  </si>
+  <si>
+    <t>KeyChongYing</t>
+  </si>
+  <si>
+    <t>KeyFeiTa</t>
+  </si>
+  <si>
+    <t>KeyNiTaiYuan</t>
+  </si>
+  <si>
+    <t>KeyTaiSui</t>
+  </si>
+  <si>
+    <t>KeyQiangChongGuai</t>
+  </si>
+  <si>
+    <t>KeyJinZhanCHongGuai</t>
+  </si>
+  <si>
+    <t>KeyGongChongGuai</t>
+  </si>
+  <si>
+    <t>KeyQiangBingGuai</t>
+  </si>
+  <si>
+    <t>KeyJinZhanBingGuai</t>
+  </si>
+  <si>
+    <t>KeyGongChengCheGuai</t>
+  </si>
+  <si>
+    <t>KeyYouChongGuai</t>
+  </si>
+  <si>
+    <t>KeyFeiChongGuai</t>
+  </si>
+  <si>
+    <t>KeyLvSeTanKeGuai</t>
+  </si>
+  <si>
+    <t>KeyFangChongGuai</t>
+  </si>
+  <si>
+    <t>KeyFangKongBingGuai</t>
+  </si>
+  <si>
+    <t>QingDianJiYaoGenSuiDeMuBiaoDanWei</t>
+  </si>
+  <si>
+    <t>请点击要跟随的目标单位</t>
+  </si>
+  <si>
+    <t>MeiYouKeYiDongDeZhanDouDanWei</t>
+  </si>
+  <si>
+    <t>没有可移动的战斗单位</t>
+  </si>
+  <si>
+    <t>QingXianXuanZhongJianZhuDanWei</t>
+  </si>
+  <si>
+    <t>请先选中活动单位</t>
+  </si>
+  <si>
+    <t>QingXianXuanZhongTaiShui</t>
+  </si>
+  <si>
+    <t>请先选中太岁</t>
+  </si>
+  <si>
+    <t>ZhanBaoBuCunZai</t>
+  </si>
+  <si>
+    <t>战报不存在</t>
+  </si>
+  <si>
+    <t>De</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 的 </t>
+  </si>
+  <si>
+    <t>JiBaiLe</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 击败了 </t>
+  </si>
+  <si>
+    <t>BeiJiBaiDanWeiShu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 被击败单位数</t>
+  </si>
+  <si>
+    <t>GongSunShi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 共损失 </t>
+  </si>
+  <si>
+    <t>JiBaiDanWeiShu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 击败单位数 </t>
+  </si>
+  <si>
+    <t>GongJiBai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 共击败 </t>
+  </si>
+  <si>
+    <t>KuangXuanXiangQiang</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 在屏幕上拖动出一个方框，选中框内所有的活动单位。&lt;br/&gt;  在左边的设置按钮（齿轮图标）里可以在&lt;color=#a0ff50&gt;正矩形框选&lt;/color&gt;模式和&lt;color=#a0ff50&gt;菱形框选&lt;/color&gt;模式之间切换</t>
+  </si>
+  <si>
+    <t>XiangQuanBuZhanDouDanWei</t>
+  </si>
+  <si>
+    <t>选中所有可移动的战斗单位</t>
+  </si>
+  <si>
+    <t>XiangQingQuanBuZhanDouDanWei</t>
+  </si>
+  <si>
+    <t>XiangQiangKongXianGongChengCheGongChong</t>
+  </si>
+  <si>
+    <t>每点击一次切换到下一个&lt;color=#a0ff50&gt;工程车&lt;/color&gt;或&lt;color=#a0ff50&gt;工虫&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>XiangQiangQuXiaoXuanZhong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    取消当前选中的单位。
+    可以防止误操作。</t>
+  </si>
+  <si>
+    <t>XiangQingQuXiao</t>
+  </si>
+  <si>
+    <t>取消当前操作</t>
+  </si>
+  <si>
+    <t>XiangQiangQiangXingZou</t>
+  </si>
+  <si>
+    <t>不理会途中遇到的敌人，强行走到目标点</t>
+  </si>
+  <si>
+    <t>XiangQingKuangXuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Drag a box on the screen to select all active units within it.
+  You can switch between &lt;color=#a0ff50&gt;Axis-Aligned Bounding Box&lt;/color&gt; mode and &lt;color=#a0ff50&gt;Diamond-Shaped Box&lt;/color&gt; mode in the settings button (gear icon) on the left.</t>
+  </si>
+  <si>
+    <t>XiangQingKongXianGongChengCheGongChong</t>
+  </si>
+  <si>
+    <t>XiangQingQuXiaoXuanZhong</t>
+  </si>
+  <si>
+    <t>XiangQingQuXiaoDianJiDiMian</t>
+  </si>
+  <si>
+    <t>Cancel current ground click action</t>
+  </si>
+  <si>
+    <t>XiangQingQueDingDianJiDianMian</t>
+  </si>
+  <si>
+    <t>确定点击地面操作</t>
+  </si>
+  <si>
+    <t>XiangQingQiangXingZou</t>
+  </si>
+  <si>
+    <t>XiangQingYuanDiJianShou</t>
+  </si>
+  <si>
+    <t>不再追击警戒距离内的敌人</t>
+  </si>
+  <si>
+    <t>XiangQingGenSui</t>
+  </si>
+  <si>
+    <t>跟随目标移动</t>
+  </si>
+  <si>
+    <t>XiangQingXunLuo</t>
+  </si>
+  <si>
+    <t>在选中的多个巡逻点之间巡逻</t>
+  </si>
+  <si>
+    <t>XiangQingLiKaiDiBao</t>
+  </si>
+  <si>
+    <t>让&lt;color=#a0ff50&gt;地堡&lt;/color&gt;里的单位都出来</t>
+  </si>
+  <si>
+    <t>XiangQingLiKaiFangChong</t>
+  </si>
+  <si>
+    <t>让&lt;color=#a0ff50&gt;房虫&lt;/color&gt;里的单位都出来</t>
+  </si>
+  <si>
+    <t>XiangQingJiJieDian</t>
+  </si>
+  <si>
+    <t>设置此建筑新产出单位的集结位置点</t>
+  </si>
+  <si>
+    <t>XiangQingGongChengCheJiJieDian</t>
+  </si>
+  <si>
+    <t>设置此建筑新产出工程车的集结位置点，如果把目标点设置到资源上，会自动采集目标资源</t>
+  </si>
+  <si>
+    <t>XiangQingGongChongJiJieDian</t>
+  </si>
+  <si>
+    <t>设置此建筑新产出工虫的集结位置点，如果把目标点设置到资源上，会自动采集目标资源</t>
+  </si>
+  <si>
+    <t>XiangQingFangChongJiJieDian</t>
+  </si>
+  <si>
+    <t>设置此建筑新产出房虫的集结位置点</t>
+  </si>
+  <si>
+    <t>XiangQingJieSuoJinZhanBing</t>
+  </si>
+  <si>
+    <t>解锁后允许在兵营里产出&lt;color=#a0ff50&gt;近战兵&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>XiangQingJieSuoQiangChong</t>
+  </si>
+  <si>
+    <t>解锁后允许幼虫蜕变为&lt;color=#a0ff50&gt;枪虫&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>XiangQingTaiSuiFenLie</t>
+  </si>
+  <si>
+    <t>分裂出一个新的太岁放置到源太岁的苔蔓(wàn)上</t>
+  </si>
+  <si>
     <t>XiangQingShanChuDanWei</t>
   </si>
   <si>
     <t>快速删除自己的单位</t>
   </si>
   <si>
-    <t>ZaiKanKan</t>
-  </si>
-  <si>
-    <t>再看看</t>
-  </si>
-  <si>
-    <t>GongJi</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>FangYu</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>YiDongSuDu</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>JingJieJvLi</t>
-  </si>
-  <si>
-    <t>警戒距离</t>
-  </si>
-  <si>
-    <t>GongJiJvLi</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
-  </si>
-  <si>
-    <t>GongJiQianYao</t>
-  </si>
-  <si>
-    <t>攻击前摇</t>
-  </si>
-  <si>
-    <t>GongJiHouYao</t>
-  </si>
-  <si>
-    <t>攻击后摇</t>
-  </si>
-  <si>
-    <t>HaoMiao</t>
-  </si>
-  <si>
-    <t>毫秒</t>
-  </si>
-  <si>
-    <t>ChuShiHP</t>
-  </si>
-  <si>
-    <t>初始HP</t>
-  </si>
-  <si>
-    <t>MiaoShu_FangDun</t>
-  </si>
-  <si>
-    <t>永久阻挡，不会损坏</t>
-  </si>
-  <si>
-    <t>MiaoShu_GongChengChe</t>
-  </si>
-  <si>
-    <t>可采集资源，可建造建筑</t>
-  </si>
-  <si>
-    <t>MiaoShu_QiangBing</t>
-  </si>
-  <si>
-    <t>远程攻击</t>
-  </si>
-  <si>
-    <t>MiaoShu_JinZhanBing</t>
-  </si>
-  <si>
-    <t>近程攻击</t>
-  </si>
-  <si>
-    <t>MiaoShu_SanSeTanKe</t>
-  </si>
-  <si>
-    <t>超远距离范围攻击，前摇较长，克制炮台。爆炸溅射可能会伤害己方单位。</t>
-  </si>
-  <si>
-    <t>MiaoShu_GongChong</t>
-  </si>
-  <si>
-    <t>可采集资源，可变成建筑</t>
-  </si>
-  <si>
-    <t>MiaoShu_FeiJi</t>
-  </si>
-  <si>
-    <t>可飞越障碍物</t>
-  </si>
-  <si>
-    <t>MiaoShu_QiangChong</t>
-  </si>
-  <si>
-    <t>MiaoShu_JinZhanChong</t>
-  </si>
-  <si>
-    <t>MiaoShu_YouChong</t>
-  </si>
-  <si>
-    <t>可蜕变为其它活动单位</t>
-  </si>
-  <si>
-    <t>MiaoShu_LvSeTanKe</t>
-  </si>
-  <si>
-    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
-  </si>
-  <si>
-    <t>MiaoShu_FangChong</t>
-  </si>
-  <si>
-    <t>可增加活动单位上限</t>
-  </si>
-  <si>
-    <t>MiaoShu_FeiChong</t>
-  </si>
-  <si>
-    <t>可飞跃障碍物</t>
-  </si>
-  <si>
-    <t>MiaoShu_YiLiaoBing</t>
-  </si>
-  <si>
-    <t>可给友方单位恢复HP</t>
-  </si>
-  <si>
-    <t>MiaoShu_FangKongBing</t>
-  </si>
-  <si>
-    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
-  </si>
-  <si>
-    <t>MiaoShu_JiDi</t>
-  </si>
-  <si>
-    <t>可产出工程车</t>
-  </si>
-  <si>
-    <t>MiaoShu_BingYing</t>
-  </si>
-  <si>
-    <t>可产出枪兵和近战兵</t>
-  </si>
-  <si>
-    <t>MiaoShu_MinFang</t>
-  </si>
-  <si>
-    <t>MiaoShu_DiBao</t>
-  </si>
-  <si>
-    <t>高HP，可派遣步兵进入地堡</t>
-  </si>
-  <si>
-    <t>MiaoShu_PaoTai</t>
-  </si>
-  <si>
-    <t>克制除了坦克以外的一切单位</t>
-  </si>
-  <si>
-    <t>MiaoShu_ChongChao</t>
-  </si>
-  <si>
-    <t>可产出幼虫</t>
-  </si>
-  <si>
-    <t>MiaoShu_JiChang</t>
-  </si>
-  <si>
-    <t>可产出飞机</t>
-  </si>
-  <si>
-    <t>MiaoShu_ZhongCheChang</t>
-  </si>
-  <si>
-    <t>可产出三色坦克</t>
-  </si>
-  <si>
-    <t>MiaoShu_ChongYing</t>
-  </si>
-  <si>
-    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>MiaoShu_FeiTa</t>
-  </si>
-  <si>
-    <t>飞虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>MiaoShu_NiTaiYuan</t>
-  </si>
-  <si>
-    <t>绿色坦克的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>MiaoShu_TaiSui</t>
-  </si>
-  <si>
-    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
-  </si>
-  <si>
-    <t>KeyTeXiao</t>
-  </si>
-  <si>
-    <t>特效</t>
-  </si>
-  <si>
-    <t>KeyShiKou</t>
-  </si>
-  <si>
-    <t>视口</t>
-  </si>
-  <si>
-    <t>KeyTaiWan</t>
-  </si>
-  <si>
-    <t>苔蔓(wàn)</t>
-  </si>
-  <si>
-    <t>KeyFangDun</t>
-  </si>
-  <si>
-    <t>KeyJingTiKuang</t>
-  </si>
-  <si>
-    <t>KeyRanQiKuang</t>
-  </si>
-  <si>
-    <t>KeyGongChengChe</t>
-  </si>
-  <si>
-    <t>工程车</t>
-  </si>
-  <si>
-    <t>KeyQiangBing</t>
-  </si>
-  <si>
-    <t>枪兵</t>
-  </si>
-  <si>
-    <t>KeyJinZhanBing</t>
-  </si>
-  <si>
-    <t>近战兵</t>
-  </si>
-  <si>
-    <t>KeySanSeTanKe</t>
-  </si>
-  <si>
-    <t>三色坦克</t>
-  </si>
-  <si>
-    <t>KeyGongChong</t>
-  </si>
-  <si>
-    <t>工虫</t>
-  </si>
-  <si>
-    <t>KeyFeiJi</t>
-  </si>
-  <si>
-    <t>飞机</t>
-  </si>
-  <si>
-    <t>KeyQiangChong</t>
-  </si>
-  <si>
-    <t>枪虫</t>
-  </si>
-  <si>
-    <t>KeyJinZhanChong</t>
-  </si>
-  <si>
-    <t>近战虫</t>
-  </si>
-  <si>
-    <t>KeyYouChong</t>
-  </si>
-  <si>
-    <t>幼虫</t>
-  </si>
-  <si>
-    <t>KeyLvSeTanKe</t>
-  </si>
-  <si>
-    <t>绿色坦克</t>
-  </si>
-  <si>
-    <t>KeyGuangCi</t>
-  </si>
-  <si>
-    <t>光刺</t>
-  </si>
-  <si>
-    <t>KeyFangChong</t>
-  </si>
-  <si>
-    <t>房虫</t>
-  </si>
-  <si>
-    <t>KeyFeiChong</t>
-  </si>
-  <si>
-    <t>飞虫</t>
-  </si>
-  <si>
-    <t>KeyYiLiaoBing</t>
-  </si>
-  <si>
-    <t>医疗兵</t>
-  </si>
-  <si>
-    <t>KeyFangKongBing</t>
-  </si>
-  <si>
-    <t>防空兵</t>
+    <t>XiangQingQu</t>
+  </si>
+  <si>
+    <t>QueDingDianJiDianMian</t>
+  </si>
+  <si>
+    <t>AttrName_3</t>
+  </si>
+  <si>
+    <t>生命</t>
+  </si>
+  <si>
+    <t>AttrName_5</t>
+  </si>
+  <si>
+    <t>前摇耗时</t>
+  </si>
+  <si>
+    <t>AttrName_7</t>
+  </si>
+  <si>
+    <t>最大生命</t>
+  </si>
+  <si>
+    <t>AttrName_8</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>DangQian</t>
+  </si>
+  <si>
+    <t>当前</t>
+  </si>
+  <si>
+    <t>ShengJiHou</t>
+  </si>
+  <si>
+    <t>升级后</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>满级</t>
+  </si>
+  <si>
+    <t>LevelFormat</t>
+  </si>
+  <si>
+    <t>{0}级</t>
+  </si>
+  <si>
+    <t>AttrName_1</t>
+  </si>
+  <si>
+    <t>AttrName_2</t>
+  </si>
+  <si>
+    <t>AttrName_4</t>
+  </si>
+  <si>
+    <t>AttrName_6</t>
+  </si>
+  <si>
+    <t>Mi</t>
+  </si>
+  <si>
+    <t>米</t>
+  </si>
+  <si>
+    <t>Miao</t>
+  </si>
+  <si>
+    <t>秒</t>
+  </si>
+  <si>
+    <t>YiDaYi_PvE</t>
+  </si>
+  <si>
+    <t>一打一（打电脑）
+&lt;size=12&gt;其他玩家可旁观您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>Ping</t>
+  </si>
+  <si>
+    <t>乒</t>
   </si>
   <si>
     <t>KeyJiJia</t>
@@ -1433,378 +1884,13 @@
     <t>机甲</t>
   </si>
   <si>
-    <t>KeyJiDi</t>
-  </si>
-  <si>
-    <t>KeyBingYing</t>
-  </si>
-  <si>
-    <t>KeyMinFang</t>
-  </si>
-  <si>
-    <t>KeyDiBao</t>
-  </si>
-  <si>
-    <t>KeyPaoTai</t>
-  </si>
-  <si>
-    <t>KeyChongChao</t>
-  </si>
-  <si>
-    <t>KeyJiChang</t>
-  </si>
-  <si>
-    <t>KeyZhongCheChang</t>
-  </si>
-  <si>
-    <t>KeyChongYing</t>
-  </si>
-  <si>
-    <t>KeyFeiTa</t>
-  </si>
-  <si>
-    <t>飞塔</t>
-  </si>
-  <si>
-    <t>KeyNiTaiYuan</t>
-  </si>
-  <si>
-    <t>KeyTaiSui</t>
-  </si>
-  <si>
-    <t>太岁</t>
-  </si>
-  <si>
-    <t>KeyQiangChongGuai</t>
-  </si>
-  <si>
-    <t>枪虫怪</t>
-  </si>
-  <si>
-    <t>KeyJinZhanCHongGuai</t>
-  </si>
-  <si>
-    <t>近战虫怪</t>
-  </si>
-  <si>
-    <t>KeyGongChongGuai</t>
-  </si>
-  <si>
-    <t>工虫怪</t>
-  </si>
-  <si>
-    <t>KeyQiangBingGuai</t>
-  </si>
-  <si>
-    <t>枪兵怪</t>
-  </si>
-  <si>
-    <t>KeyJinZhanBingGuai</t>
-  </si>
-  <si>
-    <t>近战兵怪</t>
-  </si>
-  <si>
-    <t>KeyGongChengCheGuai</t>
-  </si>
-  <si>
-    <t>工程车怪</t>
-  </si>
-  <si>
-    <t>KeyYouChongGuai</t>
-  </si>
-  <si>
-    <t>幼虫怪</t>
-  </si>
-  <si>
-    <t>KeyFeiChongGuai</t>
-  </si>
-  <si>
-    <t>飞虫怪</t>
-  </si>
-  <si>
-    <t>KeyLvSeTanKeGuai</t>
-  </si>
-  <si>
-    <t>绿色坦克怪</t>
-  </si>
-  <si>
-    <t>KeyFangChongGuai</t>
-  </si>
-  <si>
-    <t>房虫怪</t>
-  </si>
-  <si>
-    <t>KeyFangKongBingGuai</t>
-  </si>
-  <si>
-    <t>防空兵怪</t>
-  </si>
-  <si>
-    <t>Mi_Miao</t>
-  </si>
-  <si>
-    <t>米/秒</t>
-  </si>
-  <si>
-    <t>QingDianJiDiMianZhiZhiJianZhu</t>
-  </si>
-  <si>
-    <t>请点击地面放置建筑</t>
-  </si>
-  <si>
-    <t>QingDianJiYaoGenSuiDeMuBiaoDanWei</t>
-  </si>
-  <si>
-    <t>请点击要跟随的目标单位</t>
-  </si>
-  <si>
-    <t>QingDianJiDiMianZhiZhiXunLvDian</t>
-  </si>
-  <si>
-    <t>请点击地面设置巡逻点</t>
-  </si>
-  <si>
-    <t>QingDianJiDiMianZhiZhiQiangZouXingDiMuDi</t>
-  </si>
-  <si>
-    <t>强行走过程不会攻击敌人，请点击地面确定目的地</t>
-  </si>
-  <si>
-    <t>QingDianJiDiMianZhiZhiSheZhiCiJianZhuChanChuHuoDongDanWeiDeJiJiDian</t>
-  </si>
-  <si>
-    <t>请点击地面设置此建筑产出活动单位的集结点</t>
-  </si>
-  <si>
-    <t>QingZaiPingMuShangTuoDongYiKuangXuanDanWei</t>
-  </si>
-  <si>
-    <t>请在屏幕上拖动以框选单位</t>
-  </si>
-  <si>
-    <t>QingZaiXuanZhongTaiShuiDeTaiManWanShangFangZhiFenLieDeTaiShui</t>
-  </si>
-  <si>
-    <t>请在选中太岁的苔蔓(wàn)上放置分裂的太岁</t>
-  </si>
-  <si>
-    <t>SheZhi</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>JingTouTouYing</t>
-  </si>
-  <si>
-    <t>镜头投影</t>
-  </si>
-  <si>
-    <t>KuangXuanMoShi</t>
-  </si>
-  <si>
-    <t>框选模式</t>
-  </si>
-  <si>
-    <t>ShiKouFangDa</t>
-  </si>
-  <si>
-    <t>视口放大</t>
-  </si>
-  <si>
-    <t>ShiKouSuoXiao</t>
-  </si>
-  <si>
-    <t>视口缩小</t>
-  </si>
-  <si>
-    <t>DianJiZhuiJiaZuanZhong</t>
-  </si>
-  <si>
-    <t>点击单位都是追加选中</t>
-  </si>
-  <si>
-    <t>XianShiMingZi</t>
-  </si>
-  <si>
-    <t>显示名字</t>
-  </si>
-  <si>
-    <t>MingZiXianShiDanWeiLeiXing</t>
-  </si>
-  <si>
-    <t>名字里显示单位类型</t>
-  </si>
-  <si>
-    <t>LingXingKuangXuan</t>
-  </si>
-  <si>
-    <t>菱形框选</t>
-  </si>
-  <si>
-    <t>ZhengJuXingKuangXuan</t>
-  </si>
-  <si>
-    <t>正矩形框选</t>
-  </si>
-  <si>
-    <t>MoShi</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>YiQieHuanDao</t>
-  </si>
-  <si>
-    <t>已切换到</t>
-  </si>
-  <si>
-    <t>YiTianJiaWeiXunLvDian</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 已添加为巡逻点，请继续点击地面添加巡逻点，或点击</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>“</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>确定</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>”</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提交巡逻点列表</t>
-    </r>
-  </si>
-  <si>
-    <t>MeiYouKeYiDongDeZhanDouDanWei</t>
-  </si>
-  <si>
-    <t>没有可移动的战斗单位</t>
-  </si>
-  <si>
-    <t>QingXianXuanZhongJianZhuDanWei</t>
-  </si>
-  <si>
-    <t>请先选中活动单位</t>
-  </si>
-  <si>
-    <t>QingXianXuanZhongTaiShui</t>
-  </si>
-  <si>
-    <t>请先选中太岁</t>
-  </si>
-  <si>
-    <t>ZhanBaoBuCunZai</t>
-  </si>
-  <si>
-    <t>战报不存在</t>
-  </si>
-  <si>
-    <t>De</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 的 </t>
-  </si>
-  <si>
-    <t>JiBaiLe</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 击败了 </t>
-  </si>
-  <si>
-    <t>BeiJiBaiDanWeiShu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 被击败单位数</t>
-  </si>
-  <si>
-    <t>GongSunShi</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 共损失 </t>
-  </si>
-  <si>
-    <t>JiBaiDanWeiShu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 击败单位数 </t>
-  </si>
-  <si>
-    <t>GongJiBai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 共击败 </t>
-  </si>
-  <si>
-    <t>AttrName_1</t>
-  </si>
-  <si>
-    <t>AttrName_2</t>
-  </si>
-  <si>
-    <t>AttrName_3</t>
-  </si>
-  <si>
-    <t>生命</t>
-  </si>
-  <si>
-    <t>AttrName_4</t>
-  </si>
-  <si>
-    <t>AttrName_5</t>
-  </si>
-  <si>
-    <t>前摇耗时</t>
-  </si>
-  <si>
-    <t>AttrName_6</t>
-  </si>
-  <si>
-    <t>AttrName_7</t>
-  </si>
-  <si>
-    <t>最大生命</t>
-  </si>
-  <si>
-    <t>AttrName_8</t>
-  </si>
-  <si>
-    <t>能量</t>
+    <t>Key机甲</t>
+  </si>
+  <si>
+    <t>MiaoShu_JiJia</t>
+  </si>
+  <si>
+    <t>英雄单位，杀敌获得经验升级血技能</t>
   </si>
   <si>
     <t>AttrName_12</t>
@@ -1813,87 +1899,19 @@
     <t>火箭弹</t>
   </si>
   <si>
+    <t>AttrName_14</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>AttrName_15</t>
+  </si>
+  <si>
+    <t>火焰</t>
+  </si>
+  <si>
     <t>AttrName_13</t>
-  </si>
-  <si>
-    <t>AttrName_14</t>
-  </si>
-  <si>
-    <t>射程</t>
-  </si>
-  <si>
-    <t>AttrName_15</t>
-  </si>
-  <si>
-    <t>火焰</t>
-  </si>
-  <si>
-    <t>DangQian</t>
-  </si>
-  <si>
-    <t>当前</t>
-  </si>
-  <si>
-    <t>ShengJiHou</t>
-  </si>
-  <si>
-    <t>升级后</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>满级</t>
-  </si>
-  <si>
-    <t>LevelFormat</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>级</t>
-    </r>
-  </si>
-  <si>
-    <t>Mi</t>
-  </si>
-  <si>
-    <t>米</t>
-  </si>
-  <si>
-    <t>Miao</t>
-  </si>
-  <si>
-    <t>秒</t>
-  </si>
-  <si>
-    <t>Ping</t>
-  </si>
-  <si>
-    <t>乒</t>
-  </si>
-  <si>
-    <t>Key机甲</t>
-  </si>
-  <si>
-    <t>MiaoShu_JiJia</t>
-  </si>
-  <si>
-    <t>英雄单位，杀敌获得经验升级血技能</t>
   </si>
 </sst>
 </file>
@@ -1906,80 +1924,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFE394DC"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFE394DC"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1989,45 +1940,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="4"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2165,26 +2083,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2482,219 +2387,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3078,43 +2917,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C290"/>
+  <dimension ref="A1:C340"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="68.625" customWidth="1"/>
-    <col min="2" max="3" width="255.625" customWidth="1"/>
+    <col min="1" max="1" width="67.8333333333333" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3151,631 +2990,631 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="42.75" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A15" s="6" t="s">
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="B16" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A18" s="7" t="s">
+      <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="B18" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="B19" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="B20" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="B29" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="B30" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" ht="215.25" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="B32" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="B33" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" ht="28.5" spans="1:3">
-      <c r="A35" s="7" t="s">
+      <c r="B34" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" ht="28.5" spans="1:3">
-      <c r="A36" s="7" t="s">
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" ht="28.5" spans="1:3">
-      <c r="A37" s="7" t="s">
+      <c r="B36" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" s="4" customFormat="1" spans="1:3">
-      <c r="A38" s="11" t="s">
+      <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" s="4" customFormat="1" spans="1:3">
-      <c r="A39" s="4" t="s">
+      <c r="B38" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" s="4" customFormat="1" spans="1:3">
-      <c r="A40" s="4" t="s">
+      <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" s="4" customFormat="1" spans="1:3">
-      <c r="A41" s="13" t="s">
+      <c r="B40" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="17.25" spans="1:3">
-      <c r="A42" s="13" t="s">
+      <c r="B41" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" s="4" customFormat="1" ht="17.25" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" s="4" customFormat="1" ht="17.25" spans="1:3">
-      <c r="A44" s="4" t="s">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" s="4" customFormat="1" spans="1:3">
-      <c r="A45" s="4" t="s">
+      <c r="B44" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" s="4" customFormat="1" spans="1:3">
-      <c r="A46" s="4" t="s">
+      <c r="B45" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" s="4" customFormat="1" spans="1:3">
-      <c r="A47" s="4" t="s">
+      <c r="B46" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="C46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" s="4" customFormat="1" spans="1:3">
-      <c r="A48" s="4" t="s">
+      <c r="B47" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="C47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" s="4" customFormat="1" spans="1:3">
-      <c r="A49" s="4" t="s">
+      <c r="B48" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" s="4" customFormat="1" spans="1:3">
-      <c r="A50" s="4" t="s">
+      <c r="B49" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" s="4" customFormat="1" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="B50" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" s="4" customFormat="1" spans="1:3">
-      <c r="A52" s="4" t="s">
+      <c r="B51" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" s="4" customFormat="1" spans="1:3">
-      <c r="A53" s="4" t="s">
+      <c r="B52" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" s="4" customFormat="1" spans="1:3">
-      <c r="A54" s="4" t="s">
+      <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" s="4" customFormat="1" spans="1:3">
-      <c r="A55" s="4" t="s">
+      <c r="B54" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="C54" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" s="4" customFormat="1" spans="1:3">
-      <c r="A56" s="4" t="s">
+      <c r="B55" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="C55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" s="4" customFormat="1" spans="1:3">
-      <c r="A57" s="4" t="s">
+      <c r="B56" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" s="4" customFormat="1" spans="1:3">
-      <c r="A58" s="4" t="s">
+      <c r="B57" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="C57" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>115</v>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="7" t="s">
-        <v>116</v>
+      <c r="A59" t="s">
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="7" t="s">
-        <v>118</v>
+      <c r="A60" t="s">
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="7" t="s">
-        <v>120</v>
+      <c r="A61" t="s">
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4031,14 +3870,14 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" ht="42.75" spans="1:3">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4046,21 +3885,21 @@
       <c r="A88" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="89" ht="28.5" spans="1:3">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" t="s">
         <v>177</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" t="s">
         <v>177</v>
       </c>
     </row>
@@ -4229,25 +4068,25 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" ht="28.5" spans="1:3">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B105" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C105" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="106" ht="28.5" spans="1:3">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" t="s">
         <v>211</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C106" t="s">
         <v>211</v>
       </c>
     </row>
@@ -4262,729 +4101,729 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" ht="28.5" spans="1:3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B108" t="s">
         <v>215</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="7" t="s">
+      <c r="A109" t="s">
         <v>216</v>
       </c>
       <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>217</v>
       </c>
-      <c r="C109" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="7" t="s">
+      <c r="B110" t="s">
         <v>218</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
         <v>219</v>
       </c>
-      <c r="C110" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="7" t="s">
+      <c r="B111" t="s">
         <v>220</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>221</v>
       </c>
-      <c r="C111" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="7" t="s">
+      <c r="B112" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="C112" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>223</v>
       </c>
-      <c r="C112" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="7" t="s">
+      <c r="B113" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>225</v>
+      <c r="C113" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" t="s">
         <v>226</v>
       </c>
-      <c r="B114" t="s">
-        <v>227</v>
-      </c>
       <c r="C114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" t="s">
         <v>228</v>
       </c>
-      <c r="B115" t="s">
-        <v>229</v>
-      </c>
       <c r="C115" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" t="s">
         <v>230</v>
       </c>
-      <c r="B116" t="s">
-        <v>231</v>
-      </c>
       <c r="C116" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" t="s">
         <v>232</v>
       </c>
-      <c r="B117" t="s">
-        <v>233</v>
-      </c>
       <c r="C117" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" t="s">
         <v>234</v>
       </c>
-      <c r="B118" t="s">
-        <v>235</v>
-      </c>
       <c r="C118" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" t="s">
         <v>236</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
         <v>237</v>
       </c>
-      <c r="C119" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="120" ht="28.5" spans="1:3">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>238</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="C120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
         <v>239</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="121" customFormat="1" spans="1:3">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>240</v>
       </c>
-      <c r="B121" t="s">
-        <v>241</v>
-      </c>
       <c r="C121" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" t="s">
         <v>242</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
         <v>243</v>
       </c>
-      <c r="C122" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="123" customFormat="1" spans="1:3">
-      <c r="A123" t="s">
+      <c r="B123" t="s">
         <v>244</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
         <v>245</v>
       </c>
-      <c r="C123" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="124" ht="28.5" spans="1:3">
-      <c r="A124" t="s">
+      <c r="B124" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="C124" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" customFormat="1" spans="1:3">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>248</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>249</v>
       </c>
-      <c r="C125" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="126" ht="28.5" spans="1:3">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="C126" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>251</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="127" customFormat="1" spans="1:3">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>252</v>
       </c>
-      <c r="B127" t="s">
-        <v>253</v>
-      </c>
       <c r="C127" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
+        <v>253</v>
+      </c>
+      <c r="B128" t="s">
         <v>254</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
         <v>255</v>
       </c>
-      <c r="C128" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="129" customFormat="1" spans="1:3">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>256</v>
       </c>
-      <c r="B129" t="s">
-        <v>257</v>
-      </c>
       <c r="C129" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
         <v>258</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
         <v>259</v>
       </c>
-      <c r="C130" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="131" customFormat="1" spans="1:3">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>260</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
         <v>261</v>
       </c>
-      <c r="C131" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="132" ht="28.5" spans="1:3">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="C132" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="133" customFormat="1" spans="1:3">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>264</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
         <v>265</v>
       </c>
-      <c r="C133" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="134" ht="28.5" spans="1:3">
-      <c r="A134" t="s">
+      <c r="B134" t="s">
         <v>266</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="C134" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="135" customFormat="1" spans="1:3">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>268</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
         <v>269</v>
       </c>
-      <c r="C135" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="136" ht="28.5" spans="1:3">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>270</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="C136" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
         <v>271</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="137" customFormat="1" spans="1:3">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>272</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>273</v>
       </c>
-      <c r="C137" t="s">
+      <c r="B138" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="138" ht="28.5" spans="1:3">
-      <c r="A138" t="s">
+      <c r="C138" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>275</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B139" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C139" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="139" customFormat="1" spans="1:3">
-      <c r="A139" t="s">
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>277</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>278</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="140" ht="28.5" spans="1:3">
-      <c r="A140" t="s">
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
         <v>279</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B141" t="s">
         <v>280</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C141" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="141" customFormat="1" spans="1:3">
-      <c r="A141" t="s">
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
         <v>281</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B142" t="s">
         <v>282</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C142" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="142" ht="42.75" spans="1:3">
-      <c r="A142" t="s">
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
         <v>283</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B143" t="s">
         <v>284</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C143" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="143" ht="42.75" spans="1:3">
-      <c r="A143" t="s">
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
         <v>285</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B144" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C144" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="144" ht="42.75" spans="1:3">
-      <c r="A144" t="s">
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
         <v>287</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B145" t="s">
         <v>288</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C145" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="145" ht="42.75" spans="1:3">
-      <c r="A145" t="s">
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
         <v>289</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B146" t="s">
         <v>290</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C146" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="146" ht="42.75" spans="1:3">
-      <c r="A146" t="s">
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
         <v>291</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B147" t="s">
         <v>292</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C147" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="147" ht="42.75" spans="1:3">
-      <c r="A147" t="s">
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
         <v>293</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B148" t="s">
         <v>294</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C148" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="148" ht="42.75" spans="1:3">
-      <c r="A148" t="s">
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
         <v>295</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B149" t="s">
         <v>296</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C149" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="149" ht="42.75" spans="1:3">
-      <c r="A149" t="s">
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>297</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B150" t="s">
         <v>298</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C150" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="150" ht="28.5" spans="1:3">
-      <c r="A150" t="s">
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>299</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B151" t="s">
         <v>300</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C151" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="151" customFormat="1" spans="1:3">
-      <c r="A151" t="s">
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
         <v>301</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>302</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C152" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="152" ht="28.5" spans="1:3">
-      <c r="A152" t="s">
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
         <v>303</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B153" t="s">
         <v>304</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C153" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="153" customFormat="1" spans="1:3">
-      <c r="A153" t="s">
-        <v>305</v>
-      </c>
-      <c r="B153" t="s">
-        <v>306</v>
-      </c>
-      <c r="C153" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B154" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C154" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>309</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="C155" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
+      </c>
+      <c r="B155" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>311</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="C156" s="16" t="s">
-        <v>312</v>
+        <v>309</v>
+      </c>
+      <c r="B156" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>313</v>
-      </c>
-      <c r="B157" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="C157" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="B157" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>315</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
+      </c>
+      <c r="B158" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>317</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
+      </c>
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>319</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
+      </c>
+      <c r="B160" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>321</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
+      </c>
+      <c r="B161" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>323</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
+      </c>
+      <c r="B162" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>325</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
+      </c>
+      <c r="B163" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>327</v>
-      </c>
-      <c r="B164" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="C164" s="17" t="s">
-        <v>328</v>
+        <v>325</v>
+      </c>
+      <c r="B164" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>329</v>
-      </c>
-      <c r="B165" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C165" s="18" t="s">
-        <v>330</v>
+        <v>327</v>
+      </c>
+      <c r="B165" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>331</v>
-      </c>
-      <c r="B166" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="C166" s="19" t="s">
-        <v>332</v>
+        <v>329</v>
+      </c>
+      <c r="B166" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>333</v>
-      </c>
-      <c r="B167" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="C167" s="18" t="s">
-        <v>334</v>
+        <v>331</v>
+      </c>
+      <c r="B167" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>335</v>
-      </c>
-      <c r="B168" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="C168" s="18" t="s">
-        <v>336</v>
+        <v>333</v>
+      </c>
+      <c r="B168" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>337</v>
-      </c>
-      <c r="B169" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C169" s="18" t="s">
-        <v>338</v>
+        <v>335</v>
+      </c>
+      <c r="B169" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>339</v>
-      </c>
-      <c r="B170" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>340</v>
+        <v>337</v>
+      </c>
+      <c r="B170" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>341</v>
-      </c>
-      <c r="B171" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="C171" s="18" t="s">
-        <v>332</v>
+        <v>339</v>
+      </c>
+      <c r="B171" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
+        <v>341</v>
+      </c>
+      <c r="B172" t="s">
         <v>342</v>
       </c>
-      <c r="B172" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="C172" s="18" t="s">
-        <v>334</v>
+      <c r="C172" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>343</v>
       </c>
-      <c r="B173" s="18" t="s">
+      <c r="B173" t="s">
         <v>344</v>
       </c>
-      <c r="C173" s="18" t="s">
+      <c r="C173" t="s">
         <v>344</v>
       </c>
     </row>
@@ -4992,10 +4831,10 @@
       <c r="A174" t="s">
         <v>345</v>
       </c>
-      <c r="B174" s="18" t="s">
+      <c r="B174" t="s">
         <v>346</v>
       </c>
-      <c r="C174" s="18" t="s">
+      <c r="C174" t="s">
         <v>346</v>
       </c>
     </row>
@@ -5003,10 +4842,10 @@
       <c r="A175" t="s">
         <v>347</v>
       </c>
-      <c r="B175" s="18" t="s">
+      <c r="B175" t="s">
         <v>348</v>
       </c>
-      <c r="C175" s="18" t="s">
+      <c r="C175" t="s">
         <v>348</v>
       </c>
     </row>
@@ -5014,10 +4853,10 @@
       <c r="A176" t="s">
         <v>349</v>
       </c>
-      <c r="B176" s="18" t="s">
+      <c r="B176" t="s">
         <v>350</v>
       </c>
-      <c r="C176" s="18" t="s">
+      <c r="C176" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5025,10 +4864,10 @@
       <c r="A177" t="s">
         <v>351</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="B177" t="s">
         <v>352</v>
       </c>
-      <c r="C177" s="18" t="s">
+      <c r="C177" t="s">
         <v>352</v>
       </c>
     </row>
@@ -5036,10 +4875,10 @@
       <c r="A178" t="s">
         <v>353</v>
       </c>
-      <c r="B178" s="18" t="s">
+      <c r="B178" t="s">
         <v>354</v>
       </c>
-      <c r="C178" s="18" t="s">
+      <c r="C178" t="s">
         <v>354</v>
       </c>
     </row>
@@ -5047,10 +4886,10 @@
       <c r="A179" t="s">
         <v>355</v>
       </c>
-      <c r="B179" s="17" t="s">
+      <c r="B179" t="s">
         <v>356</v>
       </c>
-      <c r="C179" s="17" t="s">
+      <c r="C179" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5058,10 +4897,10 @@
       <c r="A180" t="s">
         <v>357</v>
       </c>
-      <c r="B180" s="17" t="s">
+      <c r="B180" t="s">
         <v>358</v>
       </c>
-      <c r="C180" s="17" t="s">
+      <c r="C180" t="s">
         <v>358</v>
       </c>
     </row>
@@ -5069,1221 +4908,1767 @@
       <c r="A181" t="s">
         <v>359</v>
       </c>
-      <c r="B181" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="C181" s="17" t="s">
-        <v>348</v>
+      <c r="B181" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>360</v>
-      </c>
-      <c r="B182" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="C182" s="17" t="s">
-        <v>361</v>
+      <c r="B182" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>362</v>
-      </c>
-      <c r="B183" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C183" s="17" t="s">
-        <v>363</v>
+      <c r="B183" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>364</v>
-      </c>
-      <c r="B184" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C184" s="17" t="s">
-        <v>365</v>
+      <c r="B184" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>366</v>
-      </c>
-      <c r="B185" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C185" s="17" t="s">
-        <v>367</v>
+      <c r="B185" t="s">
+        <v>368</v>
+      </c>
+      <c r="C185" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>368</v>
-      </c>
-      <c r="B186" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C186" s="17" t="s">
-        <v>369</v>
+      <c r="B186" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>370</v>
-      </c>
-      <c r="B187" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C187" s="17" t="s">
-        <v>371</v>
+      <c r="B187" t="s">
+        <v>372</v>
+      </c>
+      <c r="C187" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>372</v>
-      </c>
-      <c r="B188" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C188" s="17" t="s">
-        <v>373</v>
+      <c r="B188" t="s">
+        <v>374</v>
+      </c>
+      <c r="C188" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>374</v>
-      </c>
-      <c r="B189" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="C189" s="17" t="s">
-        <v>375</v>
+      <c r="B189" t="s">
+        <v>376</v>
+      </c>
+      <c r="C189" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>376</v>
-      </c>
-      <c r="B190" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C190" s="17" t="s">
-        <v>377</v>
+      <c r="B190" t="s">
+        <v>378</v>
+      </c>
+      <c r="C190" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="B191" s="20" t="s">
+      <c r="A191" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="20" t="s">
-        <v>379</v>
+      <c r="B191" t="s">
+        <v>380</v>
+      </c>
+      <c r="C191" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="B192" s="20" t="s">
+      <c r="A192" t="s">
         <v>381</v>
       </c>
-      <c r="C192" s="20" t="s">
-        <v>381</v>
+      <c r="B192" t="s">
+        <v>382</v>
+      </c>
+      <c r="C192" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="B193" s="21" t="s">
+      <c r="A193" t="s">
         <v>383</v>
       </c>
-      <c r="C193" s="21" t="s">
-        <v>383</v>
+      <c r="B193" t="s">
+        <v>384</v>
+      </c>
+      <c r="C193" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="B194" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C194" s="21" t="s">
-        <v>201</v>
+      <c r="A194" t="s">
+        <v>385</v>
+      </c>
+      <c r="B194" t="s">
+        <v>386</v>
+      </c>
+      <c r="C194" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="B195" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C195" s="22" t="s">
-        <v>219</v>
+      <c r="A195" t="s">
+        <v>387</v>
+      </c>
+      <c r="B195" t="s">
+        <v>388</v>
+      </c>
+      <c r="C195" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="B196" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C196" s="22" t="s">
-        <v>221</v>
+      <c r="A196" t="s">
+        <v>389</v>
+      </c>
+      <c r="B196" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="B197" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="C197" s="23" t="s">
-        <v>388</v>
+      <c r="A197" t="s">
+        <v>391</v>
+      </c>
+      <c r="B197" t="s">
+        <v>392</v>
+      </c>
+      <c r="C197" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="B198" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="C198" s="24" t="s">
-        <v>390</v>
+      <c r="A198" t="s">
+        <v>393</v>
+      </c>
+      <c r="B198" t="s">
+        <v>394</v>
+      </c>
+      <c r="C198" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="B199" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="C199" s="23" t="s">
-        <v>392</v>
+      <c r="A199" t="s">
+        <v>395</v>
+      </c>
+      <c r="B199" t="s">
+        <v>290</v>
+      </c>
+      <c r="C199" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="B200" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="C200" s="23" t="s">
-        <v>394</v>
+      <c r="A200" t="s">
+        <v>396</v>
+      </c>
+      <c r="B200" t="s">
+        <v>292</v>
+      </c>
+      <c r="C200" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="B201" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="C201" s="23" t="s">
-        <v>396</v>
+      <c r="A201" t="s">
+        <v>397</v>
+      </c>
+      <c r="B201" t="s">
+        <v>304</v>
+      </c>
+      <c r="C201" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="B202" s="23" t="s">
+      <c r="A202" t="s">
         <v>398</v>
       </c>
-      <c r="C202" s="23" t="s">
-        <v>398</v>
+      <c r="B202" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="23" t="s">
+      <c r="A203" t="s">
         <v>399</v>
       </c>
-      <c r="B203" s="23" t="s">
+      <c r="B203" t="s">
+        <v>207</v>
+      </c>
+      <c r="C203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
         <v>400</v>
       </c>
-      <c r="C203" s="23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="23" t="s">
+      <c r="B204" t="s">
+        <v>209</v>
+      </c>
+      <c r="C204" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
         <v>401</v>
       </c>
-      <c r="B204" s="23" t="s">
+      <c r="B205" t="s">
+        <v>179</v>
+      </c>
+      <c r="C205" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
         <v>402</v>
       </c>
-      <c r="C204" s="23" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="23" t="s">
+      <c r="B206" t="s">
+        <v>183</v>
+      </c>
+      <c r="C206" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
         <v>403</v>
       </c>
-      <c r="B205" s="23" t="s">
+      <c r="B207" t="s">
+        <v>181</v>
+      </c>
+      <c r="C207" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
         <v>404</v>
       </c>
-      <c r="C205" s="23" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="23" t="s">
+      <c r="B208" t="s">
+        <v>185</v>
+      </c>
+      <c r="C208" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
         <v>405</v>
       </c>
-      <c r="B206" s="23" t="s">
+      <c r="B209" t="s">
+        <v>187</v>
+      </c>
+      <c r="C209" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="23" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="23" t="s">
+      <c r="B210" t="s">
+        <v>195</v>
+      </c>
+      <c r="C210" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
         <v>407</v>
       </c>
-      <c r="B207" s="23" t="s">
+      <c r="B211" t="s">
+        <v>191</v>
+      </c>
+      <c r="C211" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="23" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="23" t="s">
+      <c r="B212" t="s">
+        <v>189</v>
+      </c>
+      <c r="C212" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" t="s">
         <v>409</v>
       </c>
-      <c r="B208" s="23" t="s">
+      <c r="B213" t="s">
+        <v>197</v>
+      </c>
+      <c r="C213" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" t="s">
         <v>410</v>
       </c>
-      <c r="C208" s="23" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" s="23" t="s">
+      <c r="B214" t="s">
+        <v>199</v>
+      </c>
+      <c r="C214" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" t="s">
         <v>411</v>
       </c>
-      <c r="B209" s="23" t="s">
+      <c r="B215" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="23" t="s">
+      <c r="C215" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
-      <c r="A210" s="23" t="s">
+    <row r="216" spans="1:3">
+      <c r="A216" t="s">
         <v>413</v>
       </c>
-      <c r="B210" s="23" t="s">
+      <c r="B216" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="23" t="s">
+      <c r="C216" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
-      <c r="A211" s="23" t="s">
+    <row r="217" spans="1:3">
+      <c r="A217" t="s">
         <v>415</v>
       </c>
-      <c r="B211" s="23" t="s">
+      <c r="B217" t="s">
         <v>416</v>
       </c>
-      <c r="C211" s="23" t="s">
+      <c r="C217" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
-      <c r="A212" s="23" t="s">
+    <row r="218" spans="1:3">
+      <c r="A218" t="s">
         <v>417</v>
       </c>
-      <c r="B212" s="23" t="s">
+      <c r="B218" t="s">
         <v>418</v>
       </c>
-      <c r="C212" s="23" t="s">
+      <c r="C218" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="21" t="s">
+    <row r="219" spans="1:3">
+      <c r="A219" t="s">
         <v>419</v>
       </c>
-      <c r="B213" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C213" s="21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="21" t="s">
+      <c r="B219" t="s">
         <v>420</v>
       </c>
-      <c r="B214" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="C214" s="21" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3">
-      <c r="A215" s="21" t="s">
+      <c r="C219" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" t="s">
         <v>421</v>
       </c>
-      <c r="B215" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="C215" s="21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216" s="21" t="s">
+      <c r="B220" t="s">
         <v>422</v>
       </c>
-      <c r="B216" s="21" t="s">
+      <c r="C220" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
+        <v>423</v>
+      </c>
+      <c r="B221" t="s">
+        <v>424</v>
+      </c>
+      <c r="C221" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
+        <v>425</v>
+      </c>
+      <c r="B222" t="s">
+        <v>426</v>
+      </c>
+      <c r="C222" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>427</v>
+      </c>
+      <c r="B223" t="s">
+        <v>428</v>
+      </c>
+      <c r="C223" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>429</v>
+      </c>
+      <c r="B224" t="s">
+        <v>430</v>
+      </c>
+      <c r="C224" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
+        <v>431</v>
+      </c>
+      <c r="B225" t="s">
+        <v>432</v>
+      </c>
+      <c r="C225" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
+        <v>433</v>
+      </c>
+      <c r="B226" t="s">
+        <v>434</v>
+      </c>
+      <c r="C226" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" t="s">
+        <v>435</v>
+      </c>
+      <c r="B227" t="s">
+        <v>436</v>
+      </c>
+      <c r="C227" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" t="s">
+        <v>437</v>
+      </c>
+      <c r="B228" t="s">
+        <v>438</v>
+      </c>
+      <c r="C228" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
+        <v>439</v>
+      </c>
+      <c r="B229" t="s">
+        <v>440</v>
+      </c>
+      <c r="C229" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
+        <v>441</v>
+      </c>
+      <c r="B230" t="s">
+        <v>442</v>
+      </c>
+      <c r="C230" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" t="s">
+        <v>443</v>
+      </c>
+      <c r="B231" t="s">
+        <v>444</v>
+      </c>
+      <c r="C231" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>445</v>
+      </c>
+      <c r="B232" t="s">
+        <v>446</v>
+      </c>
+      <c r="C232" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>447</v>
+      </c>
+      <c r="B233" t="s">
+        <v>448</v>
+      </c>
+      <c r="C233" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
+        <v>449</v>
+      </c>
+      <c r="B234" t="s">
+        <v>450</v>
+      </c>
+      <c r="C234" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
+        <v>451</v>
+      </c>
+      <c r="B235" t="s">
+        <v>334</v>
+      </c>
+      <c r="C235" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>452</v>
+      </c>
+      <c r="B236" t="s">
+        <v>336</v>
+      </c>
+      <c r="C236" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
+        <v>453</v>
+      </c>
+      <c r="B237" t="s">
+        <v>338</v>
+      </c>
+      <c r="C237" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>454</v>
+      </c>
+      <c r="B238" t="s">
         <v>193</v>
       </c>
-      <c r="C216" s="21" t="s">
+      <c r="C238" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="B217" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C217" s="21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="21" t="s">
-        <v>424</v>
-      </c>
-      <c r="B218" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="C218" s="21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="B219" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="C219" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="B220" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="C220" s="21" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="B221" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="C221" s="21" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="21" t="s">
-        <v>428</v>
-      </c>
-      <c r="B222" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="C222" s="21" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="B223" s="21" t="s">
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
+        <v>455</v>
+      </c>
+      <c r="B239" t="s">
         <v>207</v>
       </c>
-      <c r="C223" s="21" t="s">
+      <c r="C239" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="B224" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="C224" s="21" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
-      <c r="A225" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="B225" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="C225" s="23" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="B226" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="C226" s="23" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="B227" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="C227" s="23" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="B228" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="C228" s="24" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="B229" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="C229" s="23" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="B230" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="C230" s="23" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="B231" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="C231" s="23" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="23" t="s">
-        <v>447</v>
-      </c>
-      <c r="B232" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="C232" s="23" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="B233" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="C233" s="23" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="B234" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="C234" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="B235" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="C235" s="23" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="B236" t="s">
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
         <v>456</v>
       </c>
-      <c r="C236" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="7" t="s">
+      <c r="B240" t="s">
+        <v>209</v>
+      </c>
+      <c r="C240" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" t="s">
         <v>457</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B241" t="s">
+        <v>340</v>
+      </c>
+      <c r="C241" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
         <v>458</v>
       </c>
-      <c r="C237" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="7" t="s">
+      <c r="B242" t="s">
+        <v>342</v>
+      </c>
+      <c r="C242" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" t="s">
         <v>459</v>
       </c>
-      <c r="B238" t="s">
-        <v>460</v>
-      </c>
-      <c r="C238" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="B239" t="s">
-        <v>462</v>
-      </c>
-      <c r="C239" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="B240" t="s">
-        <v>464</v>
-      </c>
-      <c r="C240" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="B241" t="s">
-        <v>466</v>
-      </c>
-      <c r="C241" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="B242" t="s">
-        <v>468</v>
-      </c>
-      <c r="C242" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243" s="7" t="s">
-        <v>469</v>
-      </c>
       <c r="B243" t="s">
-        <v>470</v>
+        <v>344</v>
       </c>
       <c r="C243" t="s">
-        <v>470</v>
+        <v>344</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B244" t="s">
-        <v>472</v>
+        <v>346</v>
       </c>
       <c r="C244" t="s">
-        <v>472</v>
+        <v>346</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B245" t="s">
-        <v>474</v>
+        <v>348</v>
       </c>
       <c r="C245" t="s">
-        <v>474</v>
+        <v>348</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B246" t="s">
-        <v>476</v>
+        <v>350</v>
       </c>
       <c r="C246" t="s">
-        <v>476</v>
+        <v>350</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="B247" t="s">
-        <v>478</v>
+        <v>352</v>
       </c>
       <c r="C247" t="s">
-        <v>478</v>
+        <v>352</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B248" t="s">
-        <v>480</v>
+        <v>354</v>
       </c>
       <c r="C248" t="s">
-        <v>480</v>
+        <v>354</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="B249" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
       <c r="C249" t="s">
-        <v>482</v>
+        <v>356</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B250" t="s">
-        <v>484</v>
+        <v>358</v>
       </c>
       <c r="C250" t="s">
-        <v>484</v>
+        <v>358</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="B251" t="s">
-        <v>486</v>
+        <v>360</v>
       </c>
       <c r="C251" t="s">
-        <v>486</v>
+        <v>360</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="7" t="s">
-        <v>487</v>
+      <c r="A252" t="s">
+        <v>468</v>
       </c>
       <c r="B252" t="s">
-        <v>488</v>
+        <v>362</v>
       </c>
       <c r="C252" t="s">
-        <v>488</v>
+        <v>362</v>
       </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="7" t="s">
-        <v>489</v>
+      <c r="A253" t="s">
+        <v>469</v>
       </c>
       <c r="B253" t="s">
-        <v>490</v>
+        <v>364</v>
       </c>
       <c r="C253" t="s">
-        <v>490</v>
+        <v>364</v>
       </c>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="7" t="s">
-        <v>491</v>
+      <c r="A254" t="s">
+        <v>470</v>
       </c>
       <c r="B254" t="s">
-        <v>492</v>
+        <v>366</v>
       </c>
       <c r="C254" t="s">
-        <v>492</v>
+        <v>366</v>
       </c>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="7" t="s">
-        <v>493</v>
+      <c r="A255" t="s">
+        <v>471</v>
       </c>
       <c r="B255" t="s">
-        <v>494</v>
+        <v>368</v>
       </c>
       <c r="C255" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="256" s="4" customFormat="1" spans="1:3">
-      <c r="A256" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="C256" s="9" t="s">
-        <v>496</v>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" t="s">
+        <v>472</v>
+      </c>
+      <c r="B256" t="s">
+        <v>179</v>
+      </c>
+      <c r="C256" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>497</v>
-      </c>
-      <c r="B257" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="258" s="4" customFormat="1" spans="1:3">
-      <c r="A258" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="B258" s="25" t="s">
-        <v>500</v>
-      </c>
-      <c r="C258" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="259" s="4" customFormat="1" spans="1:3">
-      <c r="A259" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="C259" s="9" t="s">
-        <v>502</v>
+        <v>473</v>
+      </c>
+      <c r="B257" t="s">
+        <v>183</v>
+      </c>
+      <c r="C257" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>474</v>
+      </c>
+      <c r="B258" t="s">
+        <v>181</v>
+      </c>
+      <c r="C258" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
+        <v>475</v>
+      </c>
+      <c r="B259" t="s">
+        <v>185</v>
+      </c>
+      <c r="C259" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C260" s="9" t="s">
-        <v>181</v>
+      <c r="A260" t="s">
+        <v>476</v>
+      </c>
+      <c r="B260" t="s">
+        <v>187</v>
+      </c>
+      <c r="C260" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="C261" s="9" t="s">
-        <v>504</v>
+      <c r="A261" t="s">
+        <v>477</v>
+      </c>
+      <c r="B261" t="s">
+        <v>195</v>
+      </c>
+      <c r="C261" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="7" t="s">
-        <v>505</v>
+      <c r="A262" t="s">
+        <v>478</v>
       </c>
       <c r="B262" t="s">
-        <v>506</v>
+        <v>191</v>
       </c>
       <c r="C262" t="s">
-        <v>506</v>
+        <v>191</v>
       </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="7" t="s">
-        <v>507</v>
+      <c r="A263" t="s">
+        <v>479</v>
       </c>
       <c r="B263" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="C263" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C264" s="9" t="s">
-        <v>183</v>
+      <c r="A264" t="s">
+        <v>480</v>
+      </c>
+      <c r="B264" t="s">
+        <v>197</v>
+      </c>
+      <c r="C264" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="B265" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C265" s="9" t="s">
-        <v>510</v>
+      <c r="A265" t="s">
+        <v>481</v>
+      </c>
+      <c r="B265" t="s">
+        <v>370</v>
+      </c>
+      <c r="C265" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="C266" s="9" t="s">
-        <v>512</v>
+      <c r="A266" t="s">
+        <v>482</v>
+      </c>
+      <c r="B266" t="s">
+        <v>199</v>
+      </c>
+      <c r="C266" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C267" s="9" t="s">
-        <v>185</v>
+      <c r="A267" t="s">
+        <v>483</v>
+      </c>
+      <c r="B267" t="s">
+        <v>372</v>
+      </c>
+      <c r="C267" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="C268" s="9" t="s">
-        <v>514</v>
+      <c r="A268" t="s">
+        <v>484</v>
+      </c>
+      <c r="B268" t="s">
+        <v>374</v>
+      </c>
+      <c r="C268" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="C269" s="9" t="s">
-        <v>516</v>
+      <c r="A269" t="s">
+        <v>485</v>
+      </c>
+      <c r="B269" t="s">
+        <v>376</v>
+      </c>
+      <c r="C269" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="B270" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="C270" s="25" t="s">
-        <v>310</v>
+      <c r="A270" t="s">
+        <v>486</v>
+      </c>
+      <c r="B270" t="s">
+        <v>378</v>
+      </c>
+      <c r="C270" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="B271" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="C271" s="25" t="s">
-        <v>312</v>
+      <c r="A271" t="s">
+        <v>487</v>
+      </c>
+      <c r="B271" t="s">
+        <v>380</v>
+      </c>
+      <c r="C271" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="B272" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="C272" s="25" t="s">
-        <v>520</v>
+      <c r="A272" t="s">
+        <v>488</v>
+      </c>
+      <c r="B272" t="s">
+        <v>382</v>
+      </c>
+      <c r="C272" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="273" spans="1:3">
-      <c r="A273" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="B273" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="C273" s="25" t="s">
-        <v>314</v>
+      <c r="A273" t="s">
+        <v>489</v>
+      </c>
+      <c r="B273" t="s">
+        <v>384</v>
+      </c>
+      <c r="C273" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="B274" s="25" t="s">
-        <v>523</v>
-      </c>
-      <c r="C274" s="25" t="s">
-        <v>523</v>
+      <c r="A274" t="s">
+        <v>490</v>
+      </c>
+      <c r="B274" t="s">
+        <v>386</v>
+      </c>
+      <c r="C274" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="B275" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="C275" s="25" t="s">
-        <v>318</v>
+      <c r="A275" t="s">
+        <v>491</v>
+      </c>
+      <c r="B275" t="s">
+        <v>388</v>
+      </c>
+      <c r="C275" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="B276" s="25" t="s">
-        <v>526</v>
-      </c>
-      <c r="C276" s="25" t="s">
-        <v>526</v>
+      <c r="A276" t="s">
+        <v>492</v>
+      </c>
+      <c r="B276" t="s">
+        <v>390</v>
+      </c>
+      <c r="C276" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="B277" s="25" t="s">
-        <v>528</v>
-      </c>
-      <c r="C277" s="25" t="s">
-        <v>528</v>
+      <c r="A277" t="s">
+        <v>493</v>
+      </c>
+      <c r="B277" t="s">
+        <v>392</v>
+      </c>
+      <c r="C277" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="B278" t="s">
-        <v>530</v>
+        <v>394</v>
       </c>
       <c r="C278" t="s">
-        <v>530</v>
+        <v>394</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="B279" t="s">
-        <v>408</v>
+        <v>496</v>
       </c>
       <c r="C279" t="s">
-        <v>408</v>
+        <v>496</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="B280" t="s">
-        <v>533</v>
+        <v>498</v>
       </c>
       <c r="C280" t="s">
-        <v>533</v>
+        <v>498</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="B281" t="s">
-        <v>535</v>
+        <v>500</v>
       </c>
       <c r="C281" t="s">
-        <v>535</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="B282" s="25" t="s">
-        <v>537</v>
-      </c>
-      <c r="C282" s="25" t="s">
-        <v>537</v>
+      <c r="A282" t="s">
+        <v>501</v>
+      </c>
+      <c r="B282" t="s">
+        <v>502</v>
+      </c>
+      <c r="C282" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="B283" s="25" t="s">
-        <v>539</v>
-      </c>
-      <c r="C283" s="25" t="s">
-        <v>539</v>
+      <c r="A283" t="s">
+        <v>503</v>
+      </c>
+      <c r="B283" t="s">
+        <v>504</v>
+      </c>
+      <c r="C283" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="7" t="s">
-        <v>540</v>
+      <c r="A284" t="s">
+        <v>505</v>
       </c>
       <c r="B284" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="C284" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="285" s="4" customFormat="1" spans="1:3">
-      <c r="A285" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="B285" s="26" t="s">
-        <v>543</v>
-      </c>
-      <c r="C285" s="26" t="s">
-        <v>543</v>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
+        <v>507</v>
+      </c>
+      <c r="B285" t="s">
+        <v>508</v>
+      </c>
+      <c r="C285" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="B286" s="25" t="s">
-        <v>545</v>
-      </c>
-      <c r="C286" s="25" t="s">
-        <v>545</v>
+      <c r="A286" t="s">
+        <v>509</v>
+      </c>
+      <c r="B286" t="s">
+        <v>510</v>
+      </c>
+      <c r="C286" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="7" t="s">
-        <v>546</v>
+      <c r="A287" t="s">
+        <v>511</v>
       </c>
       <c r="B287" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
       <c r="C287" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>548</v>
+        <v>513</v>
       </c>
       <c r="B288" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
       <c r="C288" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>550</v>
+        <v>515</v>
       </c>
       <c r="B289" t="s">
-        <v>418</v>
+        <v>516</v>
       </c>
       <c r="C289" t="s">
-        <v>418</v>
+        <v>516</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
+        <v>517</v>
+      </c>
+      <c r="B290" t="s">
+        <v>518</v>
+      </c>
+      <c r="C290" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" t="s">
+        <v>519</v>
+      </c>
+      <c r="B291" t="s">
+        <v>520</v>
+      </c>
+      <c r="C291" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" t="s">
+        <v>521</v>
+      </c>
+      <c r="B292" t="s">
+        <v>520</v>
+      </c>
+      <c r="C292" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" t="s">
+        <v>522</v>
+      </c>
+      <c r="B293" t="s">
+        <v>523</v>
+      </c>
+      <c r="C293" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" t="s">
+        <v>524</v>
+      </c>
+      <c r="B294" t="s">
+        <v>525</v>
+      </c>
+      <c r="C294" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
+        <v>526</v>
+      </c>
+      <c r="B295" t="s">
+        <v>527</v>
+      </c>
+      <c r="C295" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
+        <v>528</v>
+      </c>
+      <c r="B296" t="s">
+        <v>529</v>
+      </c>
+      <c r="C296" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" t="s">
+        <v>530</v>
+      </c>
+      <c r="B297" t="s">
+        <v>531</v>
+      </c>
+      <c r="C297" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>532</v>
+      </c>
+      <c r="B298" t="s">
+        <v>523</v>
+      </c>
+      <c r="C298" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
+        <v>533</v>
+      </c>
+      <c r="B299" t="s">
+        <v>525</v>
+      </c>
+      <c r="C299" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
+        <v>534</v>
+      </c>
+      <c r="B300" t="s">
+        <v>535</v>
+      </c>
+      <c r="C300" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
+        <v>536</v>
+      </c>
+      <c r="B301" t="s">
+        <v>537</v>
+      </c>
+      <c r="C301" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
+        <v>538</v>
+      </c>
+      <c r="B302" t="s">
+        <v>529</v>
+      </c>
+      <c r="C302" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>539</v>
+      </c>
+      <c r="B303" t="s">
+        <v>540</v>
+      </c>
+      <c r="C303" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>541</v>
+      </c>
+      <c r="B304" t="s">
+        <v>542</v>
+      </c>
+      <c r="C304" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>543</v>
+      </c>
+      <c r="B305" t="s">
+        <v>544</v>
+      </c>
+      <c r="C305" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>545</v>
+      </c>
+      <c r="B306" t="s">
+        <v>546</v>
+      </c>
+      <c r="C306" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
+        <v>547</v>
+      </c>
+      <c r="B307" t="s">
+        <v>548</v>
+      </c>
+      <c r="C307" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>549</v>
+      </c>
+      <c r="B308" t="s">
+        <v>550</v>
+      </c>
+      <c r="C308" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
         <v>551</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B309" t="s">
         <v>552</v>
       </c>
-      <c r="C290" t="s">
+      <c r="C309" t="s">
         <v>552</v>
       </c>
     </row>
+    <row r="310" spans="1:3">
+      <c r="A310" t="s">
+        <v>553</v>
+      </c>
+      <c r="B310" t="s">
+        <v>554</v>
+      </c>
+      <c r="C310" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
+        <v>555</v>
+      </c>
+      <c r="B311" t="s">
+        <v>556</v>
+      </c>
+      <c r="C311" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" t="s">
+        <v>557</v>
+      </c>
+      <c r="B312" t="s">
+        <v>558</v>
+      </c>
+      <c r="C312" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" t="s">
+        <v>559</v>
+      </c>
+      <c r="B313" t="s">
+        <v>560</v>
+      </c>
+      <c r="C313" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
+        <v>561</v>
+      </c>
+      <c r="B314" t="s">
+        <v>562</v>
+      </c>
+      <c r="C314" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" t="s">
+        <v>563</v>
+      </c>
+      <c r="B315" t="s">
+        <v>564</v>
+      </c>
+      <c r="C315" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" t="s">
+        <v>565</v>
+      </c>
+      <c r="B316" t="s">
+        <v>527</v>
+      </c>
+      <c r="C316" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" t="s">
+        <v>566</v>
+      </c>
+      <c r="B317" t="s">
+        <v>218</v>
+      </c>
+      <c r="C317" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" t="s">
+        <v>567</v>
+      </c>
+      <c r="B318" t="s">
+        <v>568</v>
+      </c>
+      <c r="C318" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" t="s">
+        <v>569</v>
+      </c>
+      <c r="B319" t="s">
+        <v>570</v>
+      </c>
+      <c r="C319" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" t="s">
+        <v>571</v>
+      </c>
+      <c r="B320" t="s">
+        <v>572</v>
+      </c>
+      <c r="C320" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" t="s">
+        <v>573</v>
+      </c>
+      <c r="B321" t="s">
+        <v>574</v>
+      </c>
+      <c r="C321" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" t="s">
+        <v>575</v>
+      </c>
+      <c r="B322" t="s">
+        <v>576</v>
+      </c>
+      <c r="C322" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>577</v>
+      </c>
+      <c r="B323" t="s">
+        <v>578</v>
+      </c>
+      <c r="C323" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
+        <v>579</v>
+      </c>
+      <c r="B324" t="s">
+        <v>580</v>
+      </c>
+      <c r="C324" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>581</v>
+      </c>
+      <c r="B325" t="s">
+        <v>582</v>
+      </c>
+      <c r="C325" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>583</v>
+      </c>
+      <c r="B326" t="s">
+        <v>268</v>
+      </c>
+      <c r="C326" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>584</v>
+      </c>
+      <c r="B327" t="s">
+        <v>270</v>
+      </c>
+      <c r="C327" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>585</v>
+      </c>
+      <c r="B328" t="s">
+        <v>272</v>
+      </c>
+      <c r="C328" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>586</v>
+      </c>
+      <c r="B329" t="s">
+        <v>276</v>
+      </c>
+      <c r="C329" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
+        <v>587</v>
+      </c>
+      <c r="B330" t="s">
+        <v>588</v>
+      </c>
+      <c r="C330" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
+        <v>589</v>
+      </c>
+      <c r="B331" t="s">
+        <v>590</v>
+      </c>
+      <c r="C331" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" t="s">
+        <v>591</v>
+      </c>
+      <c r="B332" t="s">
+        <v>592</v>
+      </c>
+      <c r="C332" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" t="s">
+        <v>593</v>
+      </c>
+      <c r="B333" t="s">
+        <v>594</v>
+      </c>
+      <c r="C333" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" t="s">
+        <v>595</v>
+      </c>
+      <c r="B334" t="s">
+        <v>596</v>
+      </c>
+      <c r="C334" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" t="s">
+        <v>597</v>
+      </c>
+      <c r="B335" t="s">
+        <v>596</v>
+      </c>
+      <c r="C335" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" t="s">
+        <v>598</v>
+      </c>
+      <c r="B336" t="s">
+        <v>599</v>
+      </c>
+      <c r="C336" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
+        <v>600</v>
+      </c>
+      <c r="B337" t="s">
+        <v>601</v>
+      </c>
+      <c r="C337" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" t="s">
+        <v>602</v>
+      </c>
+      <c r="B338" t="s">
+        <v>603</v>
+      </c>
+      <c r="C338" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" t="s">
+        <v>604</v>
+      </c>
+      <c r="B339" t="s">
+        <v>605</v>
+      </c>
+      <c r="C339" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
+        <v>606</v>
+      </c>
+      <c r="B340" t="s">
+        <v>360</v>
+      </c>
+      <c r="C340" t="s">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B25" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
-    <hyperlink ref="C25" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C339" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>